--- a/data_raw/precio_leche_productor.xlsx
+++ b/data_raw/precio_leche_productor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/1- Producción y precios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1398" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6611D53-024D-4D00-88F1-DD35723A4858}"/>
+  <xr:revisionPtr revIDLastSave="1410" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C95AFAE-ABE1-4E9A-B758-3E547093ED10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2260,7 +2260,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="381">
+  <cellXfs count="372">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2779,22 +2779,6 @@
     <xf numFmtId="166" fontId="0" fillId="43" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="54" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="75" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2906,9 +2890,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="42" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="7" borderId="74" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="7" borderId="76" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4819,17 +4800,17 @@
       <c r="B10" s="14"/>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
-      <c r="E10" s="361" t="s">
+      <c r="E10" s="352" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="362"/>
-      <c r="G10" s="362"/>
-      <c r="H10" s="362"/>
-      <c r="I10" s="362"/>
-      <c r="J10" s="362"/>
-      <c r="K10" s="362"/>
-      <c r="L10" s="362"/>
-      <c r="M10" s="363"/>
+      <c r="F10" s="353"/>
+      <c r="G10" s="353"/>
+      <c r="H10" s="353"/>
+      <c r="I10" s="353"/>
+      <c r="J10" s="353"/>
+      <c r="K10" s="353"/>
+      <c r="L10" s="353"/>
+      <c r="M10" s="354"/>
       <c r="N10" s="17"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -4839,17 +4820,17 @@
       <c r="T10" s="19"/>
       <c r="U10" s="15"/>
       <c r="V10" s="16"/>
-      <c r="W10" s="358" t="s">
+      <c r="W10" s="349" t="s">
         <v>3</v>
       </c>
-      <c r="X10" s="359"/>
-      <c r="Y10" s="359"/>
-      <c r="Z10" s="359"/>
-      <c r="AA10" s="359"/>
-      <c r="AB10" s="359"/>
-      <c r="AC10" s="359"/>
-      <c r="AD10" s="359"/>
-      <c r="AE10" s="360"/>
+      <c r="X10" s="350"/>
+      <c r="Y10" s="350"/>
+      <c r="Z10" s="350"/>
+      <c r="AA10" s="350"/>
+      <c r="AB10" s="350"/>
+      <c r="AC10" s="350"/>
+      <c r="AD10" s="350"/>
+      <c r="AE10" s="351"/>
       <c r="AF10" s="17"/>
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
@@ -4898,55 +4879,55 @@
     </row>
     <row r="12" spans="1:37" ht="30" customHeight="1" thickBot="1">
       <c r="A12" s="6"/>
-      <c r="B12" s="295" t="s">
+      <c r="B12" s="287" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="296" t="s">
+      <c r="C12" s="288" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="297" t="s">
+      <c r="D12" s="289" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="297" t="s">
+      <c r="E12" s="289" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="297" t="s">
+      <c r="F12" s="289" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="297" t="s">
+      <c r="G12" s="289" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="297" t="s">
+      <c r="H12" s="289" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="297" t="s">
+      <c r="I12" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="297" t="s">
+      <c r="J12" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="297" t="s">
+      <c r="K12" s="289" t="s">
         <v>13</v>
       </c>
-      <c r="L12" s="297" t="s">
+      <c r="L12" s="289" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="297" t="s">
+      <c r="M12" s="289" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="298" t="s">
+      <c r="N12" s="290" t="s">
         <v>16</v>
       </c>
-      <c r="O12" s="306" t="s">
+      <c r="O12" s="298" t="s">
         <v>17</v>
       </c>
-      <c r="P12" s="307" t="s">
+      <c r="P12" s="299" t="s">
         <v>18</v>
       </c>
-      <c r="Q12" s="296" t="s">
+      <c r="Q12" s="288" t="s">
         <v>19</v>
       </c>
-      <c r="R12" s="299" t="s">
+      <c r="R12" s="291" t="s">
         <v>18</v>
       </c>
       <c r="S12" s="69"/>
@@ -5005,7 +4986,7 @@
     </row>
     <row r="13" spans="1:37" ht="14.4" customHeight="1">
       <c r="A13" s="6"/>
-      <c r="B13" s="290">
+      <c r="B13" s="282">
         <v>2002</v>
       </c>
       <c r="C13" s="31">
@@ -5044,15 +5025,15 @@
       <c r="N13" s="31">
         <v>2.7192080836477999</v>
       </c>
-      <c r="O13" s="308">
+      <c r="O13" s="300">
         <f t="shared" ref="O13:O33" si="0">AVERAGE(C13:N13)</f>
         <v>2.2904226002583559</v>
       </c>
-      <c r="P13" s="309"/>
-      <c r="Q13" s="305">
+      <c r="P13" s="301"/>
+      <c r="Q13" s="297">
         <v>2.2904226002583599</v>
       </c>
-      <c r="R13" s="300"/>
+      <c r="R13" s="292"/>
       <c r="S13" s="69"/>
       <c r="T13" s="35">
         <v>2002</v>
@@ -5106,7 +5087,7 @@
     </row>
     <row r="14" spans="1:37" ht="14.4" customHeight="1">
       <c r="A14" s="6"/>
-      <c r="B14" s="291">
+      <c r="B14" s="283">
         <v>2003</v>
       </c>
       <c r="C14" s="38">
@@ -5145,18 +5126,18 @@
       <c r="N14" s="38">
         <v>3.7211031377778698</v>
       </c>
-      <c r="O14" s="310">
+      <c r="O14" s="302">
         <f t="shared" si="0"/>
         <v>3.5526797110992443</v>
       </c>
-      <c r="P14" s="301">
+      <c r="P14" s="293">
         <f t="shared" ref="P14:P32" si="2">O14/O13-1</f>
         <v>0.55110227723849214</v>
       </c>
       <c r="Q14" s="109">
         <v>3.5526797110992399</v>
       </c>
-      <c r="R14" s="301">
+      <c r="R14" s="293">
         <f t="shared" ref="R14:R33" si="3">Q14/Q13-1</f>
         <v>0.55110227723848748</v>
       </c>
@@ -5219,7 +5200,7 @@
     </row>
     <row r="15" spans="1:37" ht="14.4" customHeight="1">
       <c r="A15" s="6"/>
-      <c r="B15" s="291">
+      <c r="B15" s="283">
         <v>2004</v>
       </c>
       <c r="C15" s="38">
@@ -5258,18 +5239,18 @@
       <c r="N15" s="38">
         <v>4.0925046293412297</v>
       </c>
-      <c r="O15" s="310">
+      <c r="O15" s="302">
         <f t="shared" si="0"/>
         <v>4.1743780455492745</v>
       </c>
-      <c r="P15" s="301">
+      <c r="P15" s="293">
         <f t="shared" si="2"/>
         <v>0.17499419734003241</v>
       </c>
       <c r="Q15" s="109">
         <v>4.1743780455492701</v>
       </c>
-      <c r="R15" s="301">
+      <c r="R15" s="293">
         <f t="shared" si="3"/>
         <v>0.17499419734003263</v>
       </c>
@@ -5332,7 +5313,7 @@
     </row>
     <row r="16" spans="1:37" ht="14.4" customHeight="1">
       <c r="A16" s="6"/>
-      <c r="B16" s="291">
+      <c r="B16" s="283">
         <v>2005</v>
       </c>
       <c r="C16" s="38">
@@ -5371,18 +5352,18 @@
       <c r="N16" s="38">
         <v>4.1492099278294603</v>
       </c>
-      <c r="O16" s="310">
+      <c r="O16" s="302">
         <f t="shared" si="0"/>
         <v>4.2268717162070173</v>
       </c>
-      <c r="P16" s="301">
+      <c r="P16" s="293">
         <f t="shared" si="2"/>
         <v>1.2575207632119279E-2</v>
       </c>
       <c r="Q16" s="109">
         <v>4.22687171620702</v>
       </c>
-      <c r="R16" s="301">
+      <c r="R16" s="293">
         <f t="shared" si="3"/>
         <v>1.2575207632121055E-2</v>
       </c>
@@ -5445,7 +5426,7 @@
     </row>
     <row r="17" spans="1:37" ht="14.4" customHeight="1">
       <c r="A17" s="6"/>
-      <c r="B17" s="291">
+      <c r="B17" s="283">
         <v>2006</v>
       </c>
       <c r="C17" s="38">
@@ -5484,18 +5465,18 @@
       <c r="N17" s="38">
         <v>3.7215982735167499</v>
       </c>
-      <c r="O17" s="310">
+      <c r="O17" s="302">
         <f t="shared" si="0"/>
         <v>4.12967634796897</v>
       </c>
-      <c r="P17" s="301">
+      <c r="P17" s="293">
         <f t="shared" si="2"/>
         <v>-2.2994634037596384E-2</v>
       </c>
       <c r="Q17" s="109">
         <v>4.12967634796897</v>
       </c>
-      <c r="R17" s="301">
+      <c r="R17" s="293">
         <f t="shared" si="3"/>
         <v>-2.299463403759705E-2</v>
       </c>
@@ -5558,7 +5539,7 @@
     </row>
     <row r="18" spans="1:37" ht="14.4" customHeight="1">
       <c r="A18" s="6"/>
-      <c r="B18" s="291">
+      <c r="B18" s="283">
         <v>2007</v>
       </c>
       <c r="C18" s="38">
@@ -5597,18 +5578,18 @@
       <c r="N18" s="38">
         <v>7.5358007999999996</v>
       </c>
-      <c r="O18" s="310">
+      <c r="O18" s="302">
         <f t="shared" si="0"/>
         <v>6.0084532018386945</v>
       </c>
-      <c r="P18" s="301">
+      <c r="P18" s="293">
         <f t="shared" si="2"/>
         <v>0.45494530214062223</v>
       </c>
       <c r="Q18" s="109">
         <v>6.00845320183869</v>
       </c>
-      <c r="R18" s="301">
+      <c r="R18" s="293">
         <f t="shared" si="3"/>
         <v>0.45494530214062112</v>
       </c>
@@ -5671,7 +5652,7 @@
     </row>
     <row r="19" spans="1:37" ht="14.4" customHeight="1">
       <c r="A19" s="6"/>
-      <c r="B19" s="291">
+      <c r="B19" s="283">
         <v>2008</v>
       </c>
       <c r="C19" s="38">
@@ -5710,18 +5691,18 @@
       <c r="N19" s="38">
         <v>4.76</v>
       </c>
-      <c r="O19" s="310">
+      <c r="O19" s="302">
         <f t="shared" si="0"/>
         <v>7.2103859089933167</v>
       </c>
-      <c r="P19" s="301">
+      <c r="P19" s="293">
         <f t="shared" si="2"/>
         <v>0.20004028770446425</v>
       </c>
       <c r="Q19" s="109">
         <v>7.2103859089933202</v>
       </c>
-      <c r="R19" s="301">
+      <c r="R19" s="293">
         <f t="shared" si="3"/>
         <v>0.2000402877044658</v>
       </c>
@@ -5784,7 +5765,7 @@
     </row>
     <row r="20" spans="1:37" ht="14.4" customHeight="1">
       <c r="A20" s="6"/>
-      <c r="B20" s="291">
+      <c r="B20" s="283">
         <v>2009</v>
       </c>
       <c r="C20" s="38">
@@ -5823,18 +5804,18 @@
       <c r="N20" s="38">
         <v>5.52</v>
       </c>
-      <c r="O20" s="310">
+      <c r="O20" s="302">
         <f t="shared" si="0"/>
         <v>5.0880669998940453</v>
       </c>
-      <c r="P20" s="301">
+      <c r="P20" s="293">
         <f t="shared" si="2"/>
         <v>-0.29434193063815917</v>
       </c>
       <c r="Q20" s="109">
         <v>5.08806699989404</v>
       </c>
-      <c r="R20" s="301">
+      <c r="R20" s="293">
         <f t="shared" si="3"/>
         <v>-0.29434193063816028</v>
       </c>
@@ -5897,7 +5878,7 @@
     </row>
     <row r="21" spans="1:37" ht="14.4" customHeight="1">
       <c r="A21" s="6"/>
-      <c r="B21" s="291">
+      <c r="B21" s="283">
         <v>2010</v>
       </c>
       <c r="C21" s="38">
@@ -5936,18 +5917,18 @@
       <c r="N21" s="38">
         <v>6.82</v>
       </c>
-      <c r="O21" s="310">
+      <c r="O21" s="302">
         <f t="shared" si="0"/>
         <v>6.413251618205102</v>
       </c>
-      <c r="P21" s="301">
+      <c r="P21" s="293">
         <f t="shared" si="2"/>
         <v>0.26044952205595018</v>
       </c>
       <c r="Q21" s="109">
         <v>6.4132516182051003</v>
       </c>
-      <c r="R21" s="301">
+      <c r="R21" s="293">
         <f t="shared" si="3"/>
         <v>0.26044952205595129</v>
       </c>
@@ -6010,7 +5991,7 @@
     </row>
     <row r="22" spans="1:37" ht="14.4" customHeight="1">
       <c r="A22" s="6"/>
-      <c r="B22" s="291">
+      <c r="B22" s="283">
         <v>2011</v>
       </c>
       <c r="C22" s="38">
@@ -6049,18 +6030,18 @@
       <c r="N22" s="38">
         <v>7.54</v>
       </c>
-      <c r="O22" s="310">
+      <c r="O22" s="302">
         <f t="shared" si="0"/>
         <v>7.9008333333333356</v>
       </c>
-      <c r="P22" s="301">
+      <c r="P22" s="293">
         <f t="shared" si="2"/>
         <v>0.23195436631637545</v>
       </c>
       <c r="Q22" s="109">
         <v>7.90083333333334</v>
       </c>
-      <c r="R22" s="301">
+      <c r="R22" s="293">
         <f t="shared" si="3"/>
         <v>0.23195436631637634</v>
       </c>
@@ -6123,7 +6104,7 @@
     </row>
     <row r="23" spans="1:37" ht="14.4" customHeight="1">
       <c r="A23" s="6"/>
-      <c r="B23" s="291">
+      <c r="B23" s="283">
         <v>2012</v>
       </c>
       <c r="C23" s="38">
@@ -6162,18 +6143,18 @@
       <c r="N23" s="38">
         <v>6.98</v>
       </c>
-      <c r="O23" s="310">
+      <c r="O23" s="302">
         <f t="shared" si="0"/>
         <v>7.6266666666666678</v>
       </c>
-      <c r="P23" s="301">
+      <c r="P23" s="293">
         <f t="shared" si="2"/>
         <v>-3.470098090918694E-2</v>
       </c>
       <c r="Q23" s="109">
         <v>7.62844568819063</v>
       </c>
-      <c r="R23" s="301">
+      <c r="R23" s="293">
         <f t="shared" si="3"/>
         <v>-3.4475812063205602E-2</v>
       </c>
@@ -6236,7 +6217,7 @@
     </row>
     <row r="24" spans="1:37" ht="14.4" customHeight="1">
       <c r="A24" s="6"/>
-      <c r="B24" s="291">
+      <c r="B24" s="283">
         <v>2013</v>
       </c>
       <c r="C24" s="38">
@@ -6275,18 +6256,18 @@
       <c r="N24" s="38">
         <v>9.32</v>
       </c>
-      <c r="O24" s="310">
+      <c r="O24" s="302">
         <f t="shared" si="0"/>
         <v>8.5416666666666661</v>
       </c>
-      <c r="P24" s="301">
+      <c r="P24" s="293">
         <f t="shared" si="2"/>
         <v>0.11997377622377603</v>
       </c>
       <c r="Q24" s="109">
         <v>8.6626261273719791</v>
       </c>
-      <c r="R24" s="301">
+      <c r="R24" s="293">
         <f t="shared" si="3"/>
         <v>0.1355689587961979</v>
       </c>
@@ -6349,7 +6330,7 @@
     </row>
     <row r="25" spans="1:37" ht="14.4" customHeight="1">
       <c r="A25" s="6"/>
-      <c r="B25" s="291">
+      <c r="B25" s="283">
         <v>2014</v>
       </c>
       <c r="C25" s="38">
@@ -6388,18 +6369,18 @@
       <c r="N25" s="38">
         <v>9.07</v>
       </c>
-      <c r="O25" s="310">
+      <c r="O25" s="302">
         <f t="shared" si="0"/>
         <v>9.9091666666666658</v>
       </c>
-      <c r="P25" s="301">
+      <c r="P25" s="293">
         <f t="shared" si="2"/>
         <v>0.16009756097560968</v>
       </c>
       <c r="Q25" s="109">
         <v>9.8467193524448096</v>
       </c>
-      <c r="R25" s="301">
+      <c r="R25" s="293">
         <f t="shared" si="3"/>
         <v>0.13668986836813346</v>
       </c>
@@ -6462,7 +6443,7 @@
     </row>
     <row r="26" spans="1:37" ht="14.4" customHeight="1">
       <c r="A26" s="6"/>
-      <c r="B26" s="291">
+      <c r="B26" s="283">
         <v>2015</v>
       </c>
       <c r="C26" s="38">
@@ -6501,18 +6482,18 @@
       <c r="N26" s="38">
         <v>7.4986725603813502</v>
       </c>
-      <c r="O26" s="310">
+      <c r="O26" s="302">
         <f t="shared" si="0"/>
         <v>8.1701585565261912</v>
       </c>
-      <c r="P26" s="301">
+      <c r="P26" s="293">
         <f t="shared" si="2"/>
         <v>-0.17549488959453119</v>
       </c>
       <c r="Q26" s="109">
         <v>8.0352379802798097</v>
       </c>
-      <c r="R26" s="301">
+      <c r="R26" s="293">
         <f t="shared" si="3"/>
         <v>-0.18396801079897063</v>
       </c>
@@ -6575,7 +6556,7 @@
     </row>
     <row r="27" spans="1:37" ht="14.4" customHeight="1">
       <c r="A27" s="6"/>
-      <c r="B27" s="291">
+      <c r="B27" s="283">
         <v>2016</v>
       </c>
       <c r="C27" s="38">
@@ -6618,18 +6599,18 @@
       <c r="N27" s="38">
         <v>9.0299999999999994</v>
       </c>
-      <c r="O27" s="310">
+      <c r="O27" s="302">
         <f t="shared" si="0"/>
         <v>8.4283333333333328</v>
       </c>
-      <c r="P27" s="301">
+      <c r="P27" s="293">
         <f t="shared" si="2"/>
         <v>3.1599726617412616E-2</v>
       </c>
       <c r="Q27" s="109">
         <v>8.5429366604999597</v>
       </c>
-      <c r="R27" s="301">
+      <c r="R27" s="293">
         <f t="shared" si="3"/>
         <v>6.3184025347619022E-2</v>
       </c>
@@ -6692,7 +6673,7 @@
     </row>
     <row r="28" spans="1:37" ht="14.4" customHeight="1">
       <c r="A28" s="6"/>
-      <c r="B28" s="292">
+      <c r="B28" s="284">
         <v>2017</v>
       </c>
       <c r="C28" s="38">
@@ -6736,18 +6717,18 @@
         <f>9.4+0.134592192182136</f>
         <v>9.5345921921821368</v>
       </c>
-      <c r="O28" s="310">
+      <c r="O28" s="302">
         <f t="shared" si="0"/>
         <v>9.7917967312294021</v>
       </c>
-      <c r="P28" s="301">
+      <c r="P28" s="293">
         <f t="shared" si="2"/>
         <v>0.16177141363212222</v>
       </c>
       <c r="Q28" s="109">
         <v>9.7220277117414398</v>
       </c>
-      <c r="R28" s="301">
+      <c r="R28" s="293">
         <f t="shared" si="3"/>
         <v>0.13801940692048587</v>
       </c>
@@ -6810,7 +6791,7 @@
     </row>
     <row r="29" spans="1:37" ht="14.4" customHeight="1">
       <c r="A29" s="6"/>
-      <c r="B29" s="292">
+      <c r="B29" s="284">
         <v>2018</v>
       </c>
       <c r="C29" s="43">
@@ -6856,18 +6837,18 @@
       <c r="N29" s="38">
         <v>9.4600000000000009</v>
       </c>
-      <c r="O29" s="310">
+      <c r="O29" s="302">
         <f t="shared" si="0"/>
         <v>9.9502278694584572</v>
       </c>
-      <c r="P29" s="301">
+      <c r="P29" s="293">
         <f t="shared" si="2"/>
         <v>1.6179986429228466E-2</v>
       </c>
       <c r="Q29" s="109">
         <v>9.9339523664547205</v>
       </c>
-      <c r="R29" s="301">
+      <c r="R29" s="293">
         <f t="shared" si="3"/>
         <v>2.1798400600868018E-2</v>
       </c>
@@ -6930,7 +6911,7 @@
     </row>
     <row r="30" spans="1:37" ht="14.4" customHeight="1">
       <c r="A30" s="6"/>
-      <c r="B30" s="292">
+      <c r="B30" s="284">
         <v>2019</v>
       </c>
       <c r="C30" s="38">
@@ -6980,18 +6961,18 @@
         <f>11.28+0.291+0.131</f>
         <v>11.702</v>
       </c>
-      <c r="O30" s="310">
+      <c r="O30" s="302">
         <f t="shared" si="0"/>
         <v>10.718916666666667</v>
       </c>
-      <c r="P30" s="301">
+      <c r="P30" s="293">
         <f t="shared" si="2"/>
         <v>7.7253386283508974E-2</v>
       </c>
       <c r="Q30" s="109">
         <v>10.7996763898577</v>
       </c>
-      <c r="R30" s="301">
+      <c r="R30" s="293">
         <f t="shared" si="3"/>
         <v>8.7147994218935709E-2</v>
       </c>
@@ -7054,7 +7035,7 @@
     </row>
     <row r="31" spans="1:37" ht="14.4" customHeight="1">
       <c r="A31" s="6"/>
-      <c r="B31" s="292">
+      <c r="B31" s="284">
         <v>2020</v>
       </c>
       <c r="C31" s="43">
@@ -7093,18 +7074,18 @@
       <c r="N31" s="43">
         <v>13.023386609161699</v>
       </c>
-      <c r="O31" s="310">
+      <c r="O31" s="302">
         <f t="shared" si="0"/>
         <v>12.528128917978966</v>
       </c>
-      <c r="P31" s="301">
+      <c r="P31" s="293">
         <f t="shared" si="2"/>
         <v>0.16878685669219995</v>
       </c>
       <c r="Q31" s="109">
         <v>12.560924151964199</v>
       </c>
-      <c r="R31" s="301">
+      <c r="R31" s="293">
         <f t="shared" si="3"/>
         <v>0.16308338310586246</v>
       </c>
@@ -7167,7 +7148,7 @@
     </row>
     <row r="32" spans="1:37" ht="14.4" customHeight="1">
       <c r="A32" s="6"/>
-      <c r="B32" s="292">
+      <c r="B32" s="284">
         <v>2021</v>
       </c>
       <c r="C32" s="43">
@@ -7206,18 +7187,18 @@
       <c r="N32" s="43">
         <v>15.7636654990532</v>
       </c>
-      <c r="O32" s="310">
+      <c r="O32" s="302">
         <f t="shared" si="0"/>
         <v>15.13867991325629</v>
       </c>
-      <c r="P32" s="301">
+      <c r="P32" s="293">
         <f t="shared" si="2"/>
         <v>0.20837517017652596</v>
       </c>
       <c r="Q32" s="109">
         <v>15.214640022568499</v>
       </c>
-      <c r="R32" s="301">
+      <c r="R32" s="293">
         <f t="shared" si="3"/>
         <v>0.21126756586531314</v>
       </c>
@@ -7280,7 +7261,7 @@
     </row>
     <row r="33" spans="1:37" ht="15" customHeight="1">
       <c r="A33" s="6"/>
-      <c r="B33" s="292">
+      <c r="B33" s="284">
         <v>2022</v>
       </c>
       <c r="C33" s="216">
@@ -7319,18 +7300,18 @@
       <c r="N33" s="216">
         <v>16.37</v>
       </c>
-      <c r="O33" s="310">
+      <c r="O33" s="302">
         <f t="shared" si="0"/>
         <v>17.16077969357335</v>
       </c>
-      <c r="P33" s="301">
+      <c r="P33" s="293">
         <f t="shared" ref="P33" si="6">O33/O32-1</f>
         <v>0.13357173755595397</v>
       </c>
       <c r="Q33" s="109">
         <v>17.128810924700328</v>
       </c>
-      <c r="R33" s="301">
+      <c r="R33" s="293">
         <f t="shared" si="3"/>
         <v>0.12581112003257799</v>
       </c>
@@ -7393,7 +7374,7 @@
     </row>
     <row r="34" spans="1:37" ht="15" customHeight="1">
       <c r="A34" s="6"/>
-      <c r="B34" s="292">
+      <c r="B34" s="284">
         <v>2023</v>
       </c>
       <c r="C34" s="216">
@@ -7432,18 +7413,18 @@
       <c r="N34" s="216">
         <v>14.07</v>
       </c>
-      <c r="O34" s="310">
+      <c r="O34" s="302">
         <f t="shared" ref="O34:O35" si="9">AVERAGE(C34:N34)</f>
         <v>16.0435142820313</v>
       </c>
-      <c r="P34" s="301">
+      <c r="P34" s="293">
         <f t="shared" ref="P34:P35" si="10">O34/O33-1</f>
         <v>-6.5105748776698169E-2</v>
       </c>
       <c r="Q34" s="109">
         <v>15.874417176752235</v>
       </c>
-      <c r="R34" s="301">
+      <c r="R34" s="293">
         <f t="shared" ref="R34:R35" si="11">Q34/Q33-1</f>
         <v>-7.3232972998681145E-2</v>
       </c>
@@ -7506,7 +7487,7 @@
     </row>
     <row r="35" spans="1:37" s="267" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="6"/>
-      <c r="B35" s="292">
+      <c r="B35" s="284">
         <v>2024</v>
       </c>
       <c r="C35" s="216">
@@ -7545,18 +7526,18 @@
       <c r="N35" s="273">
         <v>17.254154066110118</v>
       </c>
-      <c r="O35" s="310">
+      <c r="O35" s="302">
         <f t="shared" si="9"/>
         <v>16.0582209854831</v>
       </c>
-      <c r="P35" s="301">
+      <c r="P35" s="293">
         <f t="shared" si="10"/>
         <v>9.166759347900566E-4</v>
       </c>
       <c r="Q35" s="109">
         <v>16.016693895868457</v>
       </c>
-      <c r="R35" s="301">
+      <c r="R35" s="293">
         <f t="shared" si="11"/>
         <v>8.9626420631419013E-3</v>
       </c>
@@ -7619,7 +7600,7 @@
     </row>
     <row r="36" spans="1:37" s="269" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="195"/>
-      <c r="B36" s="293">
+      <c r="B36" s="285">
         <v>2025</v>
       </c>
       <c r="C36" s="273">
@@ -7658,22 +7639,22 @@
       <c r="N36" s="216">
         <v>16.66</v>
       </c>
-      <c r="O36" s="311">
+      <c r="O36" s="303">
         <v>17.531654337842706</v>
       </c>
-      <c r="P36" s="302">
+      <c r="P36" s="294">
         <f t="shared" ref="P36" si="14">O36/O35-1</f>
         <v>9.1755702807404083E-2</v>
       </c>
-      <c r="Q36" s="288">
+      <c r="Q36" s="280">
         <v>17.54025600489415</v>
       </c>
-      <c r="R36" s="302">
+      <c r="R36" s="294">
         <f>Q36/Q35-1</f>
         <v>9.5123383073375756E-2</v>
       </c>
-      <c r="S36" s="289"/>
-      <c r="T36" s="293">
+      <c r="S36" s="281"/>
+      <c r="T36" s="285">
         <v>2025</v>
       </c>
       <c r="U36" s="217">
@@ -7712,17 +7693,17 @@
       <c r="AF36" s="216">
         <v>16.66</v>
       </c>
-      <c r="AG36" s="311">
+      <c r="AG36" s="303">
         <v>17.300494927115889</v>
       </c>
-      <c r="AH36" s="302">
+      <c r="AH36" s="294">
         <f t="shared" ref="AH36:AJ36" si="15">AG36/AG35-1</f>
         <v>0.11742256916621274</v>
       </c>
-      <c r="AI36" s="288">
+      <c r="AI36" s="280">
         <v>17.315775047264474</v>
       </c>
-      <c r="AJ36" s="302">
+      <c r="AJ36" s="294">
         <f t="shared" si="15"/>
         <v>0.11761099371635853</v>
       </c>
@@ -7730,73 +7711,73 @@
     </row>
     <row r="37" spans="1:37" s="269" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A37" s="196"/>
-      <c r="B37" s="294">
+      <c r="B37" s="286">
         <v>2026</v>
       </c>
-      <c r="C37" s="354">
+      <c r="C37" s="345">
         <v>16.03</v>
       </c>
-      <c r="D37" s="355">
+      <c r="D37" s="346">
         <v>16.38</v>
       </c>
-      <c r="E37" s="355">
+      <c r="E37" s="346">
         <v>16.79</v>
       </c>
-      <c r="F37" s="353">
+      <c r="F37" s="344">
         <v>16.64</v>
       </c>
-      <c r="G37" s="353">
+      <c r="G37" s="344">
         <v>17.059999999999999</v>
       </c>
-      <c r="H37" s="339">
-        <v>16.904922634102324</v>
-      </c>
-      <c r="I37" s="339">
+      <c r="H37" s="344">
+        <v>16.86</v>
+      </c>
+      <c r="I37" s="331">
         <v>16.66087764035127</v>
       </c>
-      <c r="J37" s="303"/>
-      <c r="K37" s="303"/>
-      <c r="L37" s="303"/>
-      <c r="M37" s="303"/>
-      <c r="N37" s="303"/>
-      <c r="O37" s="312"/>
-      <c r="P37" s="304"/>
-      <c r="Q37" s="303"/>
-      <c r="R37" s="304"/>
-      <c r="S37" s="289"/>
-      <c r="T37" s="294">
+      <c r="J37" s="295"/>
+      <c r="K37" s="295"/>
+      <c r="L37" s="295"/>
+      <c r="M37" s="295"/>
+      <c r="N37" s="295"/>
+      <c r="O37" s="304"/>
+      <c r="P37" s="296"/>
+      <c r="Q37" s="295"/>
+      <c r="R37" s="296"/>
+      <c r="S37" s="281"/>
+      <c r="T37" s="286">
         <v>2026</v>
       </c>
-      <c r="U37" s="354">
+      <c r="U37" s="345">
         <v>16.03</v>
       </c>
-      <c r="V37" s="353">
+      <c r="V37" s="344">
         <v>16.38</v>
       </c>
-      <c r="W37" s="353">
+      <c r="W37" s="344">
         <v>16.79</v>
       </c>
-      <c r="X37" s="353">
+      <c r="X37" s="344">
         <v>16.64</v>
       </c>
-      <c r="Y37" s="353">
+      <c r="Y37" s="344">
         <v>17.059999999999999</v>
       </c>
-      <c r="Z37" s="339">
-        <v>16.904922634102324</v>
-      </c>
-      <c r="AA37" s="339">
+      <c r="Z37" s="344">
+        <v>16.86</v>
+      </c>
+      <c r="AA37" s="331">
         <v>16.66087764035127</v>
       </c>
-      <c r="AB37" s="303"/>
-      <c r="AC37" s="303"/>
-      <c r="AD37" s="303"/>
-      <c r="AE37" s="303"/>
-      <c r="AF37" s="303"/>
-      <c r="AG37" s="312"/>
-      <c r="AH37" s="304"/>
-      <c r="AI37" s="303"/>
-      <c r="AJ37" s="304"/>
+      <c r="AB37" s="295"/>
+      <c r="AC37" s="295"/>
+      <c r="AD37" s="295"/>
+      <c r="AE37" s="295"/>
+      <c r="AF37" s="295"/>
+      <c r="AG37" s="304"/>
+      <c r="AH37" s="296"/>
+      <c r="AI37" s="295"/>
+      <c r="AJ37" s="296"/>
       <c r="AK37" s="198"/>
     </row>
     <row r="38" spans="1:37" ht="14.4" customHeight="1">
@@ -8085,23 +8066,23 @@
     </row>
     <row r="45" spans="1:37" ht="36" customHeight="1">
       <c r="A45" s="68"/>
-      <c r="B45" s="364"/>
-      <c r="C45" s="365"/>
-      <c r="D45" s="365"/>
-      <c r="E45" s="366"/>
-      <c r="F45" s="366"/>
-      <c r="G45" s="366"/>
-      <c r="H45" s="366"/>
-      <c r="I45" s="366"/>
-      <c r="J45" s="366"/>
-      <c r="K45" s="366"/>
-      <c r="L45" s="366"/>
-      <c r="M45" s="366"/>
-      <c r="N45" s="365"/>
-      <c r="O45" s="365"/>
-      <c r="P45" s="365"/>
-      <c r="Q45" s="365"/>
-      <c r="R45" s="365"/>
+      <c r="B45" s="355"/>
+      <c r="C45" s="356"/>
+      <c r="D45" s="356"/>
+      <c r="E45" s="357"/>
+      <c r="F45" s="357"/>
+      <c r="G45" s="357"/>
+      <c r="H45" s="357"/>
+      <c r="I45" s="357"/>
+      <c r="J45" s="357"/>
+      <c r="K45" s="357"/>
+      <c r="L45" s="357"/>
+      <c r="M45" s="357"/>
+      <c r="N45" s="356"/>
+      <c r="O45" s="356"/>
+      <c r="P45" s="356"/>
+      <c r="Q45" s="356"/>
+      <c r="R45" s="356"/>
       <c r="S45" s="7"/>
       <c r="T45" s="8"/>
       <c r="U45" s="7"/>
@@ -8127,17 +8108,17 @@
       <c r="B46" s="11"/>
       <c r="C46" s="7"/>
       <c r="D46" s="69"/>
-      <c r="E46" s="361" t="s">
+      <c r="E46" s="352" t="s">
         <v>97</v>
       </c>
-      <c r="F46" s="362"/>
-      <c r="G46" s="362"/>
-      <c r="H46" s="362"/>
-      <c r="I46" s="362"/>
-      <c r="J46" s="362"/>
-      <c r="K46" s="362"/>
-      <c r="L46" s="362"/>
-      <c r="M46" s="363"/>
+      <c r="F46" s="353"/>
+      <c r="G46" s="353"/>
+      <c r="H46" s="353"/>
+      <c r="I46" s="353"/>
+      <c r="J46" s="353"/>
+      <c r="K46" s="353"/>
+      <c r="L46" s="353"/>
+      <c r="M46" s="354"/>
       <c r="N46" s="70"/>
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
@@ -8147,17 +8128,17 @@
       <c r="T46" s="71"/>
       <c r="U46" s="7"/>
       <c r="V46" s="69"/>
-      <c r="W46" s="358" t="s">
+      <c r="W46" s="349" t="s">
         <v>25</v>
       </c>
-      <c r="X46" s="359"/>
-      <c r="Y46" s="359"/>
-      <c r="Z46" s="359"/>
-      <c r="AA46" s="359"/>
-      <c r="AB46" s="359"/>
-      <c r="AC46" s="359"/>
-      <c r="AD46" s="359"/>
-      <c r="AE46" s="360"/>
+      <c r="X46" s="350"/>
+      <c r="Y46" s="350"/>
+      <c r="Z46" s="350"/>
+      <c r="AA46" s="350"/>
+      <c r="AB46" s="350"/>
+      <c r="AC46" s="350"/>
+      <c r="AD46" s="350"/>
+      <c r="AE46" s="351"/>
       <c r="AF46" s="70"/>
       <c r="AG46" s="7"/>
       <c r="AH46" s="7"/>
@@ -8206,218 +8187,218 @@
     </row>
     <row r="48" spans="1:37" ht="30" customHeight="1" thickBot="1">
       <c r="A48" s="22"/>
-      <c r="B48" s="314" t="s">
+      <c r="B48" s="306" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="315" t="s">
+      <c r="C48" s="307" t="s">
         <v>5</v>
       </c>
-      <c r="D48" s="316" t="s">
+      <c r="D48" s="308" t="s">
         <v>6</v>
       </c>
-      <c r="E48" s="316" t="s">
+      <c r="E48" s="308" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="316" t="s">
+      <c r="F48" s="308" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="316" t="s">
+      <c r="G48" s="308" t="s">
         <v>9</v>
       </c>
-      <c r="H48" s="316" t="s">
+      <c r="H48" s="308" t="s">
         <v>10</v>
       </c>
-      <c r="I48" s="316" t="s">
+      <c r="I48" s="308" t="s">
         <v>11</v>
       </c>
-      <c r="J48" s="316" t="s">
+      <c r="J48" s="308" t="s">
         <v>12</v>
       </c>
-      <c r="K48" s="316" t="s">
+      <c r="K48" s="308" t="s">
         <v>13</v>
       </c>
-      <c r="L48" s="316" t="s">
+      <c r="L48" s="308" t="s">
         <v>14</v>
       </c>
-      <c r="M48" s="316" t="s">
+      <c r="M48" s="308" t="s">
         <v>15</v>
       </c>
-      <c r="N48" s="317" t="s">
+      <c r="N48" s="309" t="s">
         <v>16</v>
       </c>
-      <c r="O48" s="315" t="s">
+      <c r="O48" s="307" t="s">
         <v>17</v>
       </c>
-      <c r="P48" s="317" t="s">
+      <c r="P48" s="309" t="s">
         <v>18</v>
       </c>
-      <c r="Q48" s="315" t="s">
+      <c r="Q48" s="307" t="s">
         <v>19</v>
       </c>
-      <c r="R48" s="317" t="s">
+      <c r="R48" s="309" t="s">
         <v>18</v>
       </c>
       <c r="S48" s="26"/>
-      <c r="T48" s="326" t="s">
+      <c r="T48" s="318" t="s">
         <v>4</v>
       </c>
-      <c r="U48" s="315" t="s">
+      <c r="U48" s="307" t="s">
         <v>5</v>
       </c>
-      <c r="V48" s="316" t="s">
+      <c r="V48" s="308" t="s">
         <v>6</v>
       </c>
-      <c r="W48" s="316" t="s">
+      <c r="W48" s="308" t="s">
         <v>7</v>
       </c>
-      <c r="X48" s="316" t="s">
+      <c r="X48" s="308" t="s">
         <v>8</v>
       </c>
-      <c r="Y48" s="316" t="s">
+      <c r="Y48" s="308" t="s">
         <v>9</v>
       </c>
-      <c r="Z48" s="316" t="s">
+      <c r="Z48" s="308" t="s">
         <v>10</v>
       </c>
-      <c r="AA48" s="316" t="s">
+      <c r="AA48" s="308" t="s">
         <v>11</v>
       </c>
-      <c r="AB48" s="316" t="s">
+      <c r="AB48" s="308" t="s">
         <v>12</v>
       </c>
-      <c r="AC48" s="316" t="s">
+      <c r="AC48" s="308" t="s">
         <v>13</v>
       </c>
-      <c r="AD48" s="316" t="s">
+      <c r="AD48" s="308" t="s">
         <v>14</v>
       </c>
-      <c r="AE48" s="316" t="s">
+      <c r="AE48" s="308" t="s">
         <v>15</v>
       </c>
-      <c r="AF48" s="317" t="s">
+      <c r="AF48" s="309" t="s">
         <v>16</v>
       </c>
-      <c r="AG48" s="315" t="s">
+      <c r="AG48" s="307" t="s">
         <v>17</v>
       </c>
-      <c r="AH48" s="317" t="s">
+      <c r="AH48" s="309" t="s">
         <v>18</v>
       </c>
-      <c r="AI48" s="315" t="s">
+      <c r="AI48" s="307" t="s">
         <v>19</v>
       </c>
-      <c r="AJ48" s="317" t="s">
+      <c r="AJ48" s="309" t="s">
         <v>18</v>
       </c>
       <c r="AK48" s="74"/>
     </row>
     <row r="49" spans="1:37" ht="14.4" customHeight="1">
       <c r="A49" s="6"/>
-      <c r="B49" s="290">
+      <c r="B49" s="282">
         <v>2002</v>
       </c>
-      <c r="C49" s="318">
+      <c r="C49" s="310">
         <v>0.128372445138622</v>
       </c>
-      <c r="D49" s="319">
+      <c r="D49" s="311">
         <v>0.13241341314473401</v>
       </c>
-      <c r="E49" s="319">
+      <c r="E49" s="311">
         <v>0.134449440735286</v>
       </c>
-      <c r="F49" s="319">
+      <c r="F49" s="311">
         <v>0.13386664897682399</v>
       </c>
-      <c r="G49" s="319">
+      <c r="G49" s="311">
         <v>0.12846626333542099</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="311">
         <v>0.123396074786911</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="311">
         <v>9.7693227490055295E-2</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="311">
         <v>9.1655866459007404E-2</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="311">
         <v>8.3379441322114903E-2</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="311">
         <v>0.102887441623494</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="311">
         <v>9.2343199852855801E-2</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="311">
         <v>9.9787452610928404E-2</v>
       </c>
-      <c r="O49" s="308">
+      <c r="O49" s="300">
         <f t="shared" ref="O49:O68" si="16">AVERAGE(C49:N49)</f>
         <v>0.1123925762896878</v>
       </c>
-      <c r="P49" s="309"/>
-      <c r="Q49" s="324">
+      <c r="P49" s="301"/>
+      <c r="Q49" s="316">
         <v>0.111068876859216</v>
       </c>
-      <c r="R49" s="309"/>
+      <c r="R49" s="301"/>
       <c r="S49" s="7"/>
-      <c r="T49" s="327">
+      <c r="T49" s="319">
         <v>2002</v>
       </c>
-      <c r="U49" s="319">
+      <c r="U49" s="311">
         <v>0.128372445138622</v>
       </c>
-      <c r="V49" s="319">
+      <c r="V49" s="311">
         <v>0.13241341314473401</v>
       </c>
-      <c r="W49" s="319">
+      <c r="W49" s="311">
         <v>0.134449440735286</v>
       </c>
-      <c r="X49" s="319">
+      <c r="X49" s="311">
         <v>0.13386664897682399</v>
       </c>
-      <c r="Y49" s="319">
+      <c r="Y49" s="311">
         <v>0.12846626333542099</v>
       </c>
-      <c r="Z49" s="319">
+      <c r="Z49" s="311">
         <v>0.123396074786911</v>
       </c>
-      <c r="AA49" s="319">
+      <c r="AA49" s="311">
         <v>9.7693227490055295E-2</v>
       </c>
-      <c r="AB49" s="319">
+      <c r="AB49" s="311">
         <v>9.1655866459007404E-2</v>
       </c>
-      <c r="AC49" s="319">
+      <c r="AC49" s="311">
         <v>8.3379441322114903E-2</v>
       </c>
-      <c r="AD49" s="319">
+      <c r="AD49" s="311">
         <v>0.102887441623494</v>
       </c>
-      <c r="AE49" s="319">
+      <c r="AE49" s="311">
         <v>9.2343199852855801E-2</v>
       </c>
-      <c r="AF49" s="319">
+      <c r="AF49" s="311">
         <v>9.9787452610928404E-2</v>
       </c>
-      <c r="AG49" s="308">
+      <c r="AG49" s="300">
         <f t="shared" ref="AG49:AG70" si="17">AVERAGE(U49:AF49)</f>
         <v>0.1123925762896878</v>
       </c>
-      <c r="AH49" s="309"/>
-      <c r="AI49" s="324">
+      <c r="AH49" s="301"/>
+      <c r="AI49" s="316">
         <v>0.111068876859216</v>
       </c>
-      <c r="AJ49" s="309"/>
-      <c r="AK49" s="325"/>
+      <c r="AJ49" s="301"/>
+      <c r="AK49" s="317"/>
     </row>
     <row r="50" spans="1:37" ht="14.4" customHeight="1">
       <c r="A50" s="6"/>
-      <c r="B50" s="291">
+      <c r="B50" s="283">
         <v>2003</v>
       </c>
-      <c r="C50" s="320">
+      <c r="C50" s="312">
         <v>9.7765298772042E-2</v>
       </c>
       <c r="D50" s="38">
@@ -8453,23 +8434,23 @@
       <c r="N50" s="38">
         <v>0.12726941438463199</v>
       </c>
-      <c r="O50" s="310">
+      <c r="O50" s="302">
         <f t="shared" si="16"/>
         <v>0.12607327169791874</v>
       </c>
-      <c r="P50" s="301">
+      <c r="P50" s="293">
         <f t="shared" ref="P50:P68" si="18">O50/O49-1</f>
         <v>0.121722411389249</v>
       </c>
       <c r="Q50" s="109">
         <v>0.12691891171451999</v>
       </c>
-      <c r="R50" s="301">
+      <c r="R50" s="293">
         <f t="shared" ref="R50:R68" si="19">Q50/Q49-1</f>
         <v>0.14270455687955241</v>
       </c>
       <c r="S50" s="7"/>
-      <c r="T50" s="328">
+      <c r="T50" s="320">
         <v>2003</v>
       </c>
       <c r="U50" s="38">
@@ -8508,18 +8489,18 @@
       <c r="AF50" s="38">
         <v>0.12726941438463199</v>
       </c>
-      <c r="AG50" s="310">
+      <c r="AG50" s="302">
         <f t="shared" si="17"/>
         <v>0.12607327169791874</v>
       </c>
-      <c r="AH50" s="301">
+      <c r="AH50" s="293">
         <f t="shared" ref="AH50:AJ71" si="20">AG50/AG49-1</f>
         <v>0.121722411389249</v>
       </c>
       <c r="AI50" s="109">
         <v>0.12691891171451999</v>
       </c>
-      <c r="AJ50" s="301">
+      <c r="AJ50" s="293">
         <f t="shared" ref="AJ50:AJ68" si="21">AI50/AI49-1</f>
         <v>0.14270455687955241</v>
       </c>
@@ -8527,10 +8508,10 @@
     </row>
     <row r="51" spans="1:37" ht="14.4" customHeight="1">
       <c r="A51" s="6"/>
-      <c r="B51" s="291">
+      <c r="B51" s="283">
         <v>2004</v>
       </c>
-      <c r="C51" s="320">
+      <c r="C51" s="312">
         <v>0.12953558976660101</v>
       </c>
       <c r="D51" s="38">
@@ -8566,23 +8547,23 @@
       <c r="N51" s="38">
         <v>0.15406206254107899</v>
       </c>
-      <c r="O51" s="310">
+      <c r="O51" s="302">
         <f t="shared" si="16"/>
         <v>0.14574238407361026</v>
       </c>
-      <c r="P51" s="301">
+      <c r="P51" s="293">
         <f t="shared" si="18"/>
         <v>0.15601334137516654</v>
       </c>
       <c r="Q51" s="109">
         <v>0.14691818383174399</v>
       </c>
-      <c r="R51" s="301">
+      <c r="R51" s="293">
         <f t="shared" si="19"/>
         <v>0.15757519385454999</v>
       </c>
       <c r="S51" s="7"/>
-      <c r="T51" s="328">
+      <c r="T51" s="320">
         <v>2004</v>
       </c>
       <c r="U51" s="38">
@@ -8621,18 +8602,18 @@
       <c r="AF51" s="38">
         <v>0.15406206254107899</v>
       </c>
-      <c r="AG51" s="310">
+      <c r="AG51" s="302">
         <f t="shared" si="17"/>
         <v>0.14574238407361026</v>
       </c>
-      <c r="AH51" s="301">
+      <c r="AH51" s="293">
         <f t="shared" si="20"/>
         <v>0.15601334137516654</v>
       </c>
       <c r="AI51" s="109">
         <v>0.14691818383174399</v>
       </c>
-      <c r="AJ51" s="301">
+      <c r="AJ51" s="293">
         <f t="shared" si="21"/>
         <v>0.15757519385454999</v>
       </c>
@@ -8640,10 +8621,10 @@
     </row>
     <row r="52" spans="1:37" ht="14.4" customHeight="1">
       <c r="A52" s="6"/>
-      <c r="B52" s="291">
+      <c r="B52" s="283">
         <v>2005</v>
       </c>
-      <c r="C52" s="320">
+      <c r="C52" s="312">
         <v>0.16157886664731599</v>
       </c>
       <c r="D52" s="38">
@@ -8679,23 +8660,23 @@
       <c r="N52" s="38">
         <v>0.17543486228190999</v>
       </c>
-      <c r="O52" s="310">
+      <c r="O52" s="302">
         <f t="shared" si="16"/>
         <v>0.17279418487470519</v>
       </c>
-      <c r="P52" s="301">
+      <c r="P52" s="293">
         <f t="shared" si="18"/>
         <v>0.18561382107919844</v>
       </c>
       <c r="Q52" s="109">
         <v>0.17319959752118</v>
       </c>
-      <c r="R52" s="301">
+      <c r="R52" s="293">
         <f t="shared" si="19"/>
         <v>0.17888468945092884</v>
       </c>
       <c r="S52" s="7"/>
-      <c r="T52" s="328">
+      <c r="T52" s="320">
         <v>2005</v>
       </c>
       <c r="U52" s="38">
@@ -8734,18 +8715,18 @@
       <c r="AF52" s="38">
         <v>0.17543486228190999</v>
       </c>
-      <c r="AG52" s="310">
+      <c r="AG52" s="302">
         <f t="shared" si="17"/>
         <v>0.17279418487470519</v>
       </c>
-      <c r="AH52" s="301">
+      <c r="AH52" s="293">
         <f t="shared" si="20"/>
         <v>0.18561382107919844</v>
       </c>
       <c r="AI52" s="109">
         <v>0.17319959752118</v>
       </c>
-      <c r="AJ52" s="301">
+      <c r="AJ52" s="293">
         <f t="shared" si="21"/>
         <v>0.17888468945092884</v>
       </c>
@@ -8753,10 +8734,10 @@
     </row>
     <row r="53" spans="1:37" ht="14.4" customHeight="1">
       <c r="A53" s="6"/>
-      <c r="B53" s="291">
+      <c r="B53" s="283">
         <v>2006</v>
       </c>
-      <c r="C53" s="320">
+      <c r="C53" s="312">
         <v>0.16471423442960301</v>
       </c>
       <c r="D53" s="38">
@@ -8792,23 +8773,23 @@
       <c r="N53" s="38">
         <v>0.15221883404297701</v>
       </c>
-      <c r="O53" s="310">
+      <c r="O53" s="302">
         <f t="shared" si="16"/>
         <v>0.17157503060509141</v>
       </c>
-      <c r="P53" s="301">
+      <c r="P53" s="293">
         <f t="shared" si="18"/>
         <v>-7.0555283471940289E-3</v>
       </c>
       <c r="Q53" s="109">
         <v>0.17005578456324</v>
       </c>
-      <c r="R53" s="301">
+      <c r="R53" s="293">
         <f t="shared" si="19"/>
         <v>-1.8151387202591795E-2</v>
       </c>
       <c r="S53" s="7"/>
-      <c r="T53" s="328">
+      <c r="T53" s="320">
         <v>2006</v>
       </c>
       <c r="U53" s="38">
@@ -8847,18 +8828,18 @@
       <c r="AF53" s="38">
         <v>0.15221883404297701</v>
       </c>
-      <c r="AG53" s="310">
+      <c r="AG53" s="302">
         <f t="shared" si="17"/>
         <v>0.17157503060509141</v>
       </c>
-      <c r="AH53" s="301">
+      <c r="AH53" s="293">
         <f t="shared" si="20"/>
         <v>-7.0555283471940289E-3</v>
       </c>
       <c r="AI53" s="109">
         <v>0.17005578456324</v>
       </c>
-      <c r="AJ53" s="301">
+      <c r="AJ53" s="293">
         <f t="shared" si="21"/>
         <v>-1.8151387202591795E-2</v>
       </c>
@@ -8866,10 +8847,10 @@
     </row>
     <row r="54" spans="1:37" ht="14.4" customHeight="1">
       <c r="A54" s="6"/>
-      <c r="B54" s="291">
+      <c r="B54" s="283">
         <v>2007</v>
       </c>
-      <c r="C54" s="320">
+      <c r="C54" s="312">
         <v>0.172722317327236</v>
       </c>
       <c r="D54" s="38">
@@ -8905,23 +8886,23 @@
       <c r="N54" s="38">
         <v>0.34739999999999999</v>
       </c>
-      <c r="O54" s="310">
+      <c r="O54" s="302">
         <f t="shared" si="16"/>
         <v>0.25817706117545897</v>
       </c>
-      <c r="P54" s="301">
+      <c r="P54" s="293">
         <f t="shared" si="18"/>
         <v>0.50474728324365903</v>
       </c>
       <c r="Q54" s="109">
         <v>0.26607669681185703</v>
       </c>
-      <c r="R54" s="301">
+      <c r="R54" s="293">
         <f t="shared" si="19"/>
         <v>0.56464361089057191</v>
       </c>
       <c r="S54" s="7"/>
-      <c r="T54" s="328">
+      <c r="T54" s="320">
         <v>2007</v>
       </c>
       <c r="U54" s="38">
@@ -8960,18 +8941,18 @@
       <c r="AF54" s="38">
         <v>0.34739999999999999</v>
       </c>
-      <c r="AG54" s="310">
+      <c r="AG54" s="302">
         <f t="shared" si="17"/>
         <v>0.25817706117545897</v>
       </c>
-      <c r="AH54" s="301">
+      <c r="AH54" s="293">
         <f t="shared" si="20"/>
         <v>0.50474728324365903</v>
       </c>
       <c r="AI54" s="109">
         <v>0.26607669681185703</v>
       </c>
-      <c r="AJ54" s="301">
+      <c r="AJ54" s="293">
         <f t="shared" si="21"/>
         <v>0.56464361089057191</v>
       </c>
@@ -8979,10 +8960,10 @@
     </row>
     <row r="55" spans="1:37" ht="14.4" customHeight="1">
       <c r="A55" s="6"/>
-      <c r="B55" s="291">
+      <c r="B55" s="283">
         <v>2008</v>
       </c>
-      <c r="C55" s="320">
+      <c r="C55" s="312">
         <v>0.37669999999999998</v>
       </c>
       <c r="D55" s="38">
@@ -9018,23 +8999,23 @@
       <c r="N55" s="38">
         <v>0.19545846507617101</v>
       </c>
-      <c r="O55" s="310">
+      <c r="O55" s="302">
         <f t="shared" si="16"/>
         <v>0.35016013743502383</v>
       </c>
-      <c r="P55" s="301">
+      <c r="P55" s="293">
         <f t="shared" si="18"/>
         <v>0.35627904292028689</v>
       </c>
       <c r="Q55" s="109">
         <v>0.33952464426128998</v>
       </c>
-      <c r="R55" s="301">
+      <c r="R55" s="293">
         <f t="shared" si="19"/>
         <v>0.27604051136191021</v>
       </c>
       <c r="S55" s="7"/>
-      <c r="T55" s="328">
+      <c r="T55" s="320">
         <v>2008</v>
       </c>
       <c r="U55" s="38">
@@ -9073,18 +9054,18 @@
       <c r="AF55" s="38">
         <v>0.19545846507617101</v>
       </c>
-      <c r="AG55" s="310">
+      <c r="AG55" s="302">
         <f t="shared" si="17"/>
         <v>0.35016013743502383</v>
       </c>
-      <c r="AH55" s="301">
+      <c r="AH55" s="293">
         <f t="shared" si="20"/>
         <v>0.35627904292028689</v>
       </c>
       <c r="AI55" s="109">
         <v>0.33952464426128998</v>
       </c>
-      <c r="AJ55" s="301">
+      <c r="AJ55" s="293">
         <f t="shared" si="21"/>
         <v>0.27604051136191021</v>
       </c>
@@ -9092,10 +9073,10 @@
     </row>
     <row r="56" spans="1:37" ht="14.4" customHeight="1">
       <c r="A56" s="6"/>
-      <c r="B56" s="291">
+      <c r="B56" s="283">
         <v>2009</v>
       </c>
-      <c r="C56" s="320">
+      <c r="C56" s="312">
         <v>0.19793902962644899</v>
       </c>
       <c r="D56" s="38">
@@ -9131,23 +9112,23 @@
       <c r="N56" s="38">
         <v>0.28016038166776602</v>
       </c>
-      <c r="O56" s="310">
+      <c r="O56" s="302">
         <f t="shared" si="16"/>
         <v>0.22706280750772864</v>
       </c>
-      <c r="P56" s="301">
+      <c r="P56" s="293">
         <f t="shared" si="18"/>
         <v>-0.35154581223608672</v>
       </c>
       <c r="Q56" s="109">
         <v>0.230222803200861</v>
       </c>
-      <c r="R56" s="301">
+      <c r="R56" s="293">
         <f t="shared" si="19"/>
         <v>-0.32192608963110469</v>
       </c>
       <c r="S56" s="7"/>
-      <c r="T56" s="328">
+      <c r="T56" s="320">
         <v>2009</v>
       </c>
       <c r="U56" s="38">
@@ -9186,18 +9167,18 @@
       <c r="AF56" s="38">
         <v>0.28016038166776602</v>
       </c>
-      <c r="AG56" s="310">
+      <c r="AG56" s="302">
         <f t="shared" si="17"/>
         <v>0.22706280750772864</v>
       </c>
-      <c r="AH56" s="301">
+      <c r="AH56" s="293">
         <f t="shared" si="20"/>
         <v>-0.35154581223608672</v>
       </c>
       <c r="AI56" s="109">
         <v>0.230222803200861</v>
       </c>
-      <c r="AJ56" s="301">
+      <c r="AJ56" s="293">
         <f t="shared" si="21"/>
         <v>-0.32192608963110469</v>
       </c>
@@ -9205,10 +9186,10 @@
     </row>
     <row r="57" spans="1:37" ht="14.4" customHeight="1">
       <c r="A57" s="6"/>
-      <c r="B57" s="291">
+      <c r="B57" s="283">
         <v>2010</v>
       </c>
-      <c r="C57" s="320">
+      <c r="C57" s="312">
         <v>0.28384066471591701</v>
       </c>
       <c r="D57" s="38">
@@ -9244,23 +9225,23 @@
       <c r="N57" s="38">
         <v>0.34142678347934902</v>
       </c>
-      <c r="O57" s="310">
+      <c r="O57" s="302">
         <f t="shared" si="16"/>
         <v>0.31984518389594646</v>
       </c>
-      <c r="P57" s="301">
+      <c r="P57" s="293">
         <f t="shared" si="18"/>
         <v>0.40861987661744092</v>
       </c>
       <c r="Q57" s="109">
         <v>0.32018425988215998</v>
       </c>
-      <c r="R57" s="301">
+      <c r="R57" s="293">
         <f t="shared" si="19"/>
         <v>0.3907582369362903</v>
       </c>
       <c r="S57" s="7"/>
-      <c r="T57" s="328">
+      <c r="T57" s="320">
         <v>2010</v>
       </c>
       <c r="U57" s="38">
@@ -9299,18 +9280,18 @@
       <c r="AF57" s="38">
         <v>0.34142678347934902</v>
       </c>
-      <c r="AG57" s="310">
+      <c r="AG57" s="302">
         <f t="shared" si="17"/>
         <v>0.31984518389594646</v>
       </c>
-      <c r="AH57" s="301">
+      <c r="AH57" s="293">
         <f t="shared" si="20"/>
         <v>0.40861987661744092</v>
       </c>
       <c r="AI57" s="109">
         <v>0.32018425988215998</v>
       </c>
-      <c r="AJ57" s="301">
+      <c r="AJ57" s="293">
         <f t="shared" si="21"/>
         <v>0.3907582369362903</v>
       </c>
@@ -9318,10 +9299,10 @@
     </row>
     <row r="58" spans="1:37" ht="14.4" customHeight="1">
       <c r="A58" s="6"/>
-      <c r="B58" s="291">
+      <c r="B58" s="283">
         <v>2011</v>
       </c>
-      <c r="C58" s="320">
+      <c r="C58" s="312">
         <v>0.36149431074413502</v>
       </c>
       <c r="D58" s="38">
@@ -9357,23 +9338,23 @@
       <c r="N58" s="38">
         <v>0.37756634952428603</v>
       </c>
-      <c r="O58" s="310">
+      <c r="O58" s="302">
         <f t="shared" si="16"/>
         <v>0.40988489993539617</v>
       </c>
-      <c r="P58" s="301">
+      <c r="P58" s="293">
         <f t="shared" si="18"/>
         <v>0.28151030740153926</v>
       </c>
       <c r="Q58" s="109">
         <v>0.40811971389561402</v>
       </c>
-      <c r="R58" s="301">
+      <c r="R58" s="293">
         <f t="shared" si="19"/>
         <v>0.27464015266027642</v>
       </c>
       <c r="S58" s="7"/>
-      <c r="T58" s="328">
+      <c r="T58" s="320">
         <v>2011</v>
       </c>
       <c r="U58" s="38">
@@ -9412,18 +9393,18 @@
       <c r="AF58" s="38">
         <v>0.37756634952428603</v>
       </c>
-      <c r="AG58" s="310">
+      <c r="AG58" s="302">
         <f t="shared" si="17"/>
         <v>0.40988489993539617</v>
       </c>
-      <c r="AH58" s="301">
+      <c r="AH58" s="293">
         <f t="shared" si="20"/>
         <v>0.28151030740153926</v>
       </c>
       <c r="AI58" s="109">
         <v>0.40811971389561402</v>
       </c>
-      <c r="AJ58" s="301">
+      <c r="AJ58" s="293">
         <f t="shared" si="21"/>
         <v>0.27464015266027642</v>
       </c>
@@ -9431,10 +9412,10 @@
     </row>
     <row r="59" spans="1:37" ht="14.4" customHeight="1">
       <c r="A59" s="6"/>
-      <c r="B59" s="291">
+      <c r="B59" s="283">
         <v>2012</v>
       </c>
-      <c r="C59" s="320">
+      <c r="C59" s="312">
         <v>0.41477707006369402</v>
       </c>
       <c r="D59" s="38">
@@ -9470,23 +9451,23 @@
       <c r="N59" s="38">
         <v>0.36158309158723601</v>
       </c>
-      <c r="O59" s="310">
+      <c r="O59" s="302">
         <f t="shared" si="16"/>
         <v>0.37623027710926316</v>
       </c>
-      <c r="P59" s="301">
+      <c r="P59" s="293">
         <f t="shared" si="18"/>
         <v>-8.2107496107901246E-2</v>
       </c>
       <c r="Q59" s="109">
         <v>0.37415475605069098</v>
       </c>
-      <c r="R59" s="301">
+      <c r="R59" s="293">
         <f t="shared" si="19"/>
         <v>-8.3223026696550018E-2</v>
       </c>
       <c r="S59" s="7"/>
-      <c r="T59" s="328">
+      <c r="T59" s="320">
         <v>2012</v>
       </c>
       <c r="U59" s="38">
@@ -9525,18 +9506,18 @@
       <c r="AF59" s="38">
         <v>0.36158309158723601</v>
       </c>
-      <c r="AG59" s="310">
+      <c r="AG59" s="302">
         <f t="shared" si="17"/>
         <v>0.37623027710926316</v>
       </c>
-      <c r="AH59" s="301">
+      <c r="AH59" s="293">
         <f t="shared" si="20"/>
         <v>-8.2107496107901246E-2</v>
       </c>
       <c r="AI59" s="109">
         <v>0.37415475605069098</v>
       </c>
-      <c r="AJ59" s="301">
+      <c r="AJ59" s="293">
         <f t="shared" si="21"/>
         <v>-8.3223026696550018E-2</v>
       </c>
@@ -9544,10 +9525,10 @@
     </row>
     <row r="60" spans="1:37" ht="14.4" customHeight="1">
       <c r="A60" s="6"/>
-      <c r="B60" s="291">
+      <c r="B60" s="283">
         <v>2013</v>
       </c>
-      <c r="C60" s="320">
+      <c r="C60" s="312">
         <v>0.37665562913907302</v>
       </c>
       <c r="D60" s="38">
@@ -9583,23 +9564,23 @@
       <c r="N60" s="38">
         <v>0.43626831437532199</v>
       </c>
-      <c r="O60" s="310">
+      <c r="O60" s="302">
         <f t="shared" si="16"/>
         <v>0.41706190783437663</v>
       </c>
-      <c r="P60" s="301">
+      <c r="P60" s="293">
         <f t="shared" si="18"/>
         <v>0.10852829559290189</v>
       </c>
       <c r="Q60" s="109">
         <v>0.41937677654780298</v>
       </c>
-      <c r="R60" s="301">
+      <c r="R60" s="293">
         <f t="shared" si="19"/>
         <v>0.12086448124953209</v>
       </c>
       <c r="S60" s="7"/>
-      <c r="T60" s="328">
+      <c r="T60" s="320">
         <v>2013</v>
       </c>
       <c r="U60" s="38">
@@ -9638,18 +9619,18 @@
       <c r="AF60" s="38">
         <v>0.43626831437532199</v>
       </c>
-      <c r="AG60" s="310">
+      <c r="AG60" s="302">
         <f t="shared" si="17"/>
         <v>0.41706190783437663</v>
       </c>
-      <c r="AH60" s="301">
+      <c r="AH60" s="293">
         <f t="shared" si="20"/>
         <v>0.10852829559290189</v>
       </c>
       <c r="AI60" s="109">
         <v>0.41937677654780298</v>
       </c>
-      <c r="AJ60" s="301">
+      <c r="AJ60" s="293">
         <f t="shared" si="21"/>
         <v>0.12086448124953209</v>
       </c>
@@ -9657,10 +9638,10 @@
     </row>
     <row r="61" spans="1:37" ht="14.4" customHeight="1">
       <c r="A61" s="6"/>
-      <c r="B61" s="291">
+      <c r="B61" s="283">
         <v>2014</v>
       </c>
-      <c r="C61" s="320">
+      <c r="C61" s="312">
         <v>0.45068341337273699</v>
       </c>
       <c r="D61" s="38">
@@ -9696,23 +9677,23 @@
       <c r="N61" s="38">
         <v>0.37623926660306101</v>
       </c>
-      <c r="O61" s="310">
+      <c r="O61" s="302">
         <f t="shared" si="16"/>
         <v>0.42728878975602091</v>
       </c>
-      <c r="P61" s="301">
+      <c r="P61" s="293">
         <f t="shared" si="18"/>
         <v>2.4521256268039693E-2</v>
       </c>
       <c r="Q61" s="109">
         <v>0.42264838225031998</v>
       </c>
-      <c r="R61" s="301">
+      <c r="R61" s="293">
         <f t="shared" si="19"/>
         <v>7.8011131885937779E-3</v>
       </c>
       <c r="S61" s="7"/>
-      <c r="T61" s="328">
+      <c r="T61" s="320">
         <v>2014</v>
       </c>
       <c r="U61" s="38">
@@ -9751,18 +9732,18 @@
       <c r="AF61" s="38">
         <v>0.37623926660306101</v>
       </c>
-      <c r="AG61" s="310">
+      <c r="AG61" s="302">
         <f t="shared" si="17"/>
         <v>0.42728878975602091</v>
       </c>
-      <c r="AH61" s="301">
+      <c r="AH61" s="293">
         <f t="shared" si="20"/>
         <v>2.4521256268039693E-2</v>
       </c>
       <c r="AI61" s="109">
         <v>0.42264838225031998</v>
       </c>
-      <c r="AJ61" s="301">
+      <c r="AJ61" s="293">
         <f t="shared" si="21"/>
         <v>7.8011131885937779E-3</v>
       </c>
@@ -9770,10 +9751,10 @@
     </row>
     <row r="62" spans="1:37" ht="14.4" customHeight="1">
       <c r="A62" s="6"/>
-      <c r="B62" s="291">
+      <c r="B62" s="283">
         <v>2015</v>
       </c>
-      <c r="C62" s="320">
+      <c r="C62" s="312">
         <v>0.368269398970548</v>
       </c>
       <c r="D62" s="38">
@@ -9809,23 +9790,23 @@
       <c r="N62" s="38">
         <v>0.25180230222905797</v>
       </c>
-      <c r="O62" s="310">
+      <c r="O62" s="302">
         <f t="shared" si="16"/>
         <v>0.30198126267403297</v>
       </c>
-      <c r="P62" s="301">
+      <c r="P62" s="293">
         <f t="shared" si="18"/>
         <v>-0.2932619111152851</v>
       </c>
       <c r="Q62" s="109">
         <v>0.29484615928250701</v>
       </c>
-      <c r="R62" s="301">
+      <c r="R62" s="293">
         <f t="shared" si="19"/>
         <v>-0.30238427102773136</v>
       </c>
       <c r="S62" s="7"/>
-      <c r="T62" s="328">
+      <c r="T62" s="320">
         <v>2015</v>
       </c>
       <c r="U62" s="38">
@@ -9864,18 +9845,18 @@
       <c r="AF62" s="38">
         <v>0.25180230222905797</v>
       </c>
-      <c r="AG62" s="310">
+      <c r="AG62" s="302">
         <f t="shared" si="17"/>
         <v>0.30198126267403297</v>
       </c>
-      <c r="AH62" s="301">
+      <c r="AH62" s="293">
         <f t="shared" si="20"/>
         <v>-0.2932619111152851</v>
       </c>
       <c r="AI62" s="109">
         <v>0.29484615928250701</v>
       </c>
-      <c r="AJ62" s="301">
+      <c r="AJ62" s="293">
         <f t="shared" si="21"/>
         <v>-0.30238427102773136</v>
       </c>
@@ -9883,10 +9864,10 @@
     </row>
     <row r="63" spans="1:37" ht="14.4" customHeight="1">
       <c r="A63" s="6"/>
-      <c r="B63" s="291">
+      <c r="B63" s="283">
         <v>2016</v>
       </c>
-      <c r="C63" s="320">
+      <c r="C63" s="312">
         <v>0.23784801090271901</v>
       </c>
       <c r="D63" s="38">
@@ -9922,23 +9903,23 @@
       <c r="N63" s="38">
         <v>0.31310679611650499</v>
       </c>
-      <c r="O63" s="310">
+      <c r="O63" s="302">
         <f t="shared" si="16"/>
         <v>0.280697814641022</v>
       </c>
-      <c r="P63" s="301">
+      <c r="P63" s="293">
         <f t="shared" si="18"/>
         <v>-7.0479366317455661E-2</v>
       </c>
       <c r="Q63" s="109">
         <v>0.28465729192526501</v>
       </c>
-      <c r="R63" s="301">
+      <c r="R63" s="293">
         <f t="shared" si="19"/>
         <v>-3.45565544487203E-2</v>
       </c>
       <c r="S63" s="7"/>
-      <c r="T63" s="328">
+      <c r="T63" s="320">
         <v>2016</v>
       </c>
       <c r="U63" s="38">
@@ -9977,18 +9958,18 @@
       <c r="AF63" s="38">
         <v>0.31310679611650499</v>
       </c>
-      <c r="AG63" s="310">
+      <c r="AG63" s="302">
         <f t="shared" si="17"/>
         <v>0.28068374369017574</v>
       </c>
-      <c r="AH63" s="301">
+      <c r="AH63" s="293">
         <f t="shared" si="20"/>
         <v>-7.0525961760900313E-2</v>
       </c>
       <c r="AI63" s="109">
         <v>0.28465729192526501</v>
       </c>
-      <c r="AJ63" s="301">
+      <c r="AJ63" s="293">
         <f t="shared" si="21"/>
         <v>-3.45565544487203E-2</v>
       </c>
@@ -9996,10 +9977,10 @@
     </row>
     <row r="64" spans="1:37" ht="14.4" customHeight="1">
       <c r="A64" s="6"/>
-      <c r="B64" s="292">
+      <c r="B64" s="284">
         <v>2017</v>
       </c>
-      <c r="C64" s="320">
+      <c r="C64" s="312">
         <v>0.31561287616650902</v>
       </c>
       <c r="D64" s="38">
@@ -10035,23 +10016,23 @@
       <c r="N64" s="43">
         <v>0.33014515900907698</v>
       </c>
-      <c r="O64" s="310">
+      <c r="O64" s="302">
         <f t="shared" si="16"/>
         <v>0.34158503910440524</v>
       </c>
-      <c r="P64" s="301">
+      <c r="P64" s="293">
         <f t="shared" si="18"/>
         <v>0.21691378160977326</v>
       </c>
       <c r="Q64" s="109">
         <v>0.33864532425546001</v>
       </c>
-      <c r="R64" s="301">
+      <c r="R64" s="293">
         <f t="shared" si="19"/>
         <v>0.18965975529750079</v>
       </c>
       <c r="S64" s="7"/>
-      <c r="T64" s="292">
+      <c r="T64" s="284">
         <v>2017</v>
       </c>
       <c r="U64" s="38">
@@ -10090,18 +10071,18 @@
       <c r="AF64" s="38">
         <v>0.32548476454293601</v>
       </c>
-      <c r="AG64" s="310">
+      <c r="AG64" s="302">
         <f t="shared" si="17"/>
         <v>0.3396558141457085</v>
       </c>
-      <c r="AH64" s="301">
+      <c r="AH64" s="293">
         <f t="shared" si="20"/>
         <v>0.21010148176100762</v>
       </c>
       <c r="AI64" s="109">
         <v>0.33864532425546001</v>
       </c>
-      <c r="AJ64" s="301">
+      <c r="AJ64" s="293">
         <f t="shared" si="21"/>
         <v>0.18965975529750079</v>
       </c>
@@ -10109,10 +10090,10 @@
     </row>
     <row r="65" spans="1:37" ht="14.4" customHeight="1">
       <c r="A65" s="6"/>
-      <c r="B65" s="292">
+      <c r="B65" s="284">
         <v>2018</v>
       </c>
-      <c r="C65" s="321">
+      <c r="C65" s="313">
         <v>0.33646605035115601</v>
       </c>
       <c r="D65" s="43">
@@ -10148,23 +10129,23 @@
       <c r="N65" s="38">
         <v>0.29366114111876801</v>
       </c>
-      <c r="O65" s="310">
+      <c r="O65" s="302">
         <f t="shared" si="16"/>
         <v>0.32510052452938304</v>
       </c>
-      <c r="P65" s="301">
+      <c r="P65" s="293">
         <f t="shared" si="18"/>
         <v>-4.8258889260029081E-2</v>
       </c>
       <c r="Q65" s="109">
         <v>0.32229745657187803</v>
       </c>
-      <c r="R65" s="301">
+      <c r="R65" s="293">
         <f t="shared" si="19"/>
         <v>-4.8274305040307719E-2</v>
       </c>
       <c r="S65" s="7"/>
-      <c r="T65" s="292">
+      <c r="T65" s="284">
         <v>2018</v>
       </c>
       <c r="U65" s="38">
@@ -10203,18 +10184,18 @@
       <c r="AF65" s="38">
         <v>0.29366114111876801</v>
       </c>
-      <c r="AG65" s="310">
+      <c r="AG65" s="302">
         <f t="shared" si="17"/>
         <v>0.32232426477271819</v>
       </c>
-      <c r="AH65" s="301">
+      <c r="AH65" s="293">
         <f t="shared" si="20"/>
         <v>-5.1026800222990665E-2</v>
       </c>
       <c r="AI65" s="109">
         <v>0.319792087502487</v>
       </c>
-      <c r="AJ65" s="301">
+      <c r="AJ65" s="293">
         <f t="shared" si="21"/>
         <v>-5.5672514582693289E-2</v>
       </c>
@@ -10222,10 +10203,10 @@
     </row>
     <row r="66" spans="1:37" ht="14.4" customHeight="1">
       <c r="A66" s="6"/>
-      <c r="B66" s="292">
+      <c r="B66" s="284">
         <v>2019</v>
       </c>
-      <c r="C66" s="320">
+      <c r="C66" s="312">
         <v>0.28928155101539998</v>
       </c>
       <c r="D66" s="43">
@@ -10261,23 +10242,23 @@
       <c r="N66" s="43">
         <v>0.31134761207928702</v>
       </c>
-      <c r="O66" s="310">
+      <c r="O66" s="302">
         <f t="shared" si="16"/>
         <v>0.30388347724426534</v>
       </c>
-      <c r="P66" s="301">
+      <c r="P66" s="293">
         <f t="shared" si="18"/>
         <v>-6.5263036151146148E-2</v>
       </c>
       <c r="Q66" s="109">
         <v>0.30410499557590598</v>
       </c>
-      <c r="R66" s="301">
+      <c r="R66" s="293">
         <f t="shared" si="19"/>
         <v>-5.6446182323237837E-2</v>
       </c>
       <c r="S66" s="7"/>
-      <c r="T66" s="292">
+      <c r="T66" s="284">
         <v>2019</v>
       </c>
       <c r="U66" s="38">
@@ -10316,18 +10297,18 @@
       <c r="AF66" s="38">
         <v>0.30011972861513903</v>
       </c>
-      <c r="AG66" s="310">
+      <c r="AG66" s="302">
         <f t="shared" si="17"/>
         <v>0.30030095056130407</v>
       </c>
-      <c r="AH66" s="301">
+      <c r="AH66" s="293">
         <f t="shared" si="20"/>
         <v>-6.8326578599174126E-2</v>
       </c>
       <c r="AI66" s="109">
         <v>0.30046525273006602</v>
       </c>
-      <c r="AJ66" s="301">
+      <c r="AJ66" s="293">
         <f t="shared" si="21"/>
         <v>-6.0435625294420925E-2</v>
       </c>
@@ -10335,10 +10316,10 @@
     </row>
     <row r="67" spans="1:37" ht="14.4" customHeight="1">
       <c r="A67" s="6"/>
-      <c r="B67" s="292">
+      <c r="B67" s="284">
         <v>2020</v>
       </c>
-      <c r="C67" s="321">
+      <c r="C67" s="313">
         <v>0.32060012768674201</v>
       </c>
       <c r="D67" s="43">
@@ -10374,23 +10355,23 @@
       <c r="N67" s="43">
         <v>0.30718432420892799</v>
       </c>
-      <c r="O67" s="310">
+      <c r="O67" s="302">
         <f t="shared" si="16"/>
         <v>0.29883788698993852</v>
       </c>
-      <c r="P67" s="301">
+      <c r="P67" s="293">
         <f t="shared" si="18"/>
         <v>-1.6603700537068389E-2</v>
       </c>
       <c r="Q67" s="109">
         <v>0.29874128780418102</v>
       </c>
-      <c r="R67" s="301">
+      <c r="R67" s="293">
         <f t="shared" si="19"/>
         <v>-1.7637683858390152E-2</v>
       </c>
       <c r="S67" s="7"/>
-      <c r="T67" s="292">
+      <c r="T67" s="284">
         <v>2020</v>
       </c>
       <c r="U67" s="38">
@@ -10429,18 +10410,18 @@
       <c r="AF67" s="38">
         <v>0.30238701764317399</v>
       </c>
-      <c r="AG67" s="310">
+      <c r="AG67" s="302">
         <f t="shared" si="17"/>
         <v>0.29431054299789616</v>
       </c>
-      <c r="AH67" s="301">
+      <c r="AH67" s="293">
         <f t="shared" si="20"/>
         <v>-1.994801399133439E-2</v>
       </c>
       <c r="AI67" s="109">
         <v>0.29427909496996102</v>
       </c>
-      <c r="AJ67" s="301">
+      <c r="AJ67" s="293">
         <f t="shared" si="21"/>
         <v>-2.0588596198384934E-2</v>
       </c>
@@ -10448,10 +10429,10 @@
     </row>
     <row r="68" spans="1:37" ht="14.4" customHeight="1">
       <c r="A68" s="6"/>
-      <c r="B68" s="292">
+      <c r="B68" s="284">
         <v>2021</v>
       </c>
-      <c r="C68" s="321">
+      <c r="C68" s="313">
         <v>0.32000371068925998</v>
       </c>
       <c r="D68" s="43">
@@ -10487,23 +10468,23 @@
       <c r="N68" s="43">
         <v>0.35563825152968298</v>
       </c>
-      <c r="O68" s="310">
+      <c r="O68" s="302">
         <f t="shared" si="16"/>
         <v>0.34754642545719666</v>
       </c>
-      <c r="P68" s="301">
+      <c r="P68" s="293">
         <f t="shared" si="18"/>
         <v>0.16299318322009859</v>
       </c>
       <c r="Q68" s="109">
         <v>0.34930739892531898</v>
       </c>
-      <c r="R68" s="301">
+      <c r="R68" s="293">
         <f t="shared" si="19"/>
         <v>0.16926388546026172</v>
       </c>
       <c r="S68" s="7"/>
-      <c r="T68" s="292">
+      <c r="T68" s="284">
         <v>2021</v>
       </c>
       <c r="U68" s="38">
@@ -10542,18 +10523,18 @@
       <c r="AF68" s="38">
         <v>0.35059221658206402</v>
       </c>
-      <c r="AG68" s="310">
+      <c r="AG68" s="302">
         <f t="shared" si="17"/>
         <v>0.34130711707315192</v>
       </c>
-      <c r="AH68" s="301">
+      <c r="AH68" s="293">
         <f t="shared" si="20"/>
         <v>0.15968362395903601</v>
       </c>
       <c r="AI68" s="109">
         <v>0.34281851132805602</v>
       </c>
-      <c r="AJ68" s="301">
+      <c r="AJ68" s="293">
         <f t="shared" si="21"/>
         <v>0.16494347436758883</v>
       </c>
@@ -10561,10 +10542,10 @@
     </row>
     <row r="69" spans="1:37" ht="15" customHeight="1">
       <c r="A69" s="6"/>
-      <c r="B69" s="292">
+      <c r="B69" s="284">
         <v>2022</v>
       </c>
-      <c r="C69" s="322">
+      <c r="C69" s="314">
         <v>0.35740761541053578</v>
       </c>
       <c r="D69" s="216">
@@ -10600,23 +10581,23 @@
       <c r="N69" s="216">
         <v>0.41877718086467125</v>
       </c>
-      <c r="O69" s="310">
+      <c r="O69" s="302">
         <f t="shared" ref="O69:O70" si="22">AVERAGE(C69:N69)</f>
         <v>0.41743976379395514</v>
       </c>
-      <c r="P69" s="301">
+      <c r="P69" s="293">
         <f t="shared" ref="P69:R71" si="23">O69/O68-1</f>
         <v>0.2011050415633362</v>
       </c>
       <c r="Q69" s="109">
         <v>0.41771464653289508</v>
       </c>
-      <c r="R69" s="301">
+      <c r="R69" s="293">
         <f t="shared" si="23"/>
         <v>0.19583681255546903</v>
       </c>
       <c r="S69" s="7"/>
-      <c r="T69" s="292">
+      <c r="T69" s="284">
         <v>2022</v>
       </c>
       <c r="U69" s="216">
@@ -10655,18 +10636,18 @@
       <c r="AF69" s="216">
         <v>0.41877718086467125</v>
       </c>
-      <c r="AG69" s="310">
+      <c r="AG69" s="302">
         <f t="shared" si="17"/>
         <v>0.41742128709586246</v>
       </c>
-      <c r="AH69" s="301">
+      <c r="AH69" s="293">
         <f t="shared" si="20"/>
         <v>0.22300786070744927</v>
       </c>
       <c r="AI69" s="109">
         <v>0.41769963796243853</v>
       </c>
-      <c r="AJ69" s="301">
+      <c r="AJ69" s="293">
         <f t="shared" si="20"/>
         <v>0.21842789744433011</v>
       </c>
@@ -10674,10 +10655,10 @@
     </row>
     <row r="70" spans="1:37" ht="15" customHeight="1">
       <c r="A70" s="6"/>
-      <c r="B70" s="292">
+      <c r="B70" s="284">
         <v>2023</v>
       </c>
-      <c r="C70" s="322">
+      <c r="C70" s="314">
         <v>0.42070786573909508</v>
       </c>
       <c r="D70" s="216">
@@ -10713,23 +10694,23 @@
       <c r="N70" s="216">
         <v>0.35760517976105632</v>
       </c>
-      <c r="O70" s="310">
+      <c r="O70" s="302">
         <f t="shared" si="22"/>
         <v>0.41293831242055351</v>
       </c>
-      <c r="P70" s="301">
+      <c r="P70" s="293">
         <f t="shared" si="23"/>
         <v>-1.0783475279138699E-2</v>
       </c>
       <c r="Q70" s="109">
         <v>0.40869661057801471</v>
       </c>
-      <c r="R70" s="301">
+      <c r="R70" s="293">
         <f t="shared" si="23"/>
         <v>-2.1588986715528558E-2</v>
       </c>
       <c r="S70" s="7"/>
-      <c r="T70" s="292">
+      <c r="T70" s="284">
         <v>2023</v>
       </c>
       <c r="U70" s="216">
@@ -10768,18 +10749,18 @@
       <c r="AF70" s="216">
         <v>0.35760517976105632</v>
       </c>
-      <c r="AG70" s="310">
+      <c r="AG70" s="302">
         <f t="shared" si="17"/>
         <v>0.41230917455664856</v>
       </c>
-      <c r="AH70" s="301">
+      <c r="AH70" s="293">
         <f t="shared" ref="AH70" si="24">AG70/AG69-1</f>
         <v>-1.224688988618805E-2</v>
       </c>
       <c r="AI70" s="109">
         <v>0.40795872687437473</v>
       </c>
-      <c r="AJ70" s="301">
+      <c r="AJ70" s="293">
         <f t="shared" si="20"/>
         <v>-2.3320372350765006E-2</v>
       </c>
@@ -10787,10 +10768,10 @@
     </row>
     <row r="71" spans="1:37" ht="15" customHeight="1">
       <c r="A71" s="6"/>
-      <c r="B71" s="292">
+      <c r="B71" s="284">
         <v>2024</v>
       </c>
-      <c r="C71" s="322">
+      <c r="C71" s="314">
         <v>0.36287250025893542</v>
       </c>
       <c r="D71" s="270">
@@ -10826,23 +10807,23 @@
       <c r="N71" s="273">
         <v>0.3920596711152291</v>
       </c>
-      <c r="O71" s="310">
+      <c r="O71" s="302">
         <f t="shared" ref="O71" si="25">AVERAGE(C71:N71)</f>
         <v>0.39957892641892118</v>
       </c>
-      <c r="P71" s="301">
+      <c r="P71" s="293">
         <f>+O71/O70-1</f>
         <v>-3.2352013847595229E-2</v>
       </c>
       <c r="Q71" s="109">
         <v>0.39658372155990007</v>
       </c>
-      <c r="R71" s="301">
+      <c r="R71" s="293">
         <f t="shared" si="23"/>
         <v>-2.9637850436252777E-2</v>
       </c>
       <c r="S71" s="7"/>
-      <c r="T71" s="292">
+      <c r="T71" s="284">
         <v>2024</v>
       </c>
       <c r="U71" s="216">
@@ -10881,18 +10862,18 @@
       <c r="AF71" s="216">
         <v>0.37389075763421575</v>
       </c>
-      <c r="AG71" s="310">
+      <c r="AG71" s="302">
         <f t="shared" ref="AG71" si="26">AVERAGE(U71:AF71)</f>
         <v>0.38533965945345633</v>
       </c>
-      <c r="AH71" s="301">
+      <c r="AH71" s="293">
         <f t="shared" ref="AH71" si="27">AG71/AG70-1</f>
         <v>-6.5410902224507295E-2</v>
       </c>
       <c r="AI71" s="109">
         <v>0.38363202432610127</v>
       </c>
-      <c r="AJ71" s="301">
+      <c r="AJ71" s="293">
         <f t="shared" si="20"/>
         <v>-5.9630303130553064E-2</v>
       </c>
@@ -10900,10 +10881,10 @@
     </row>
     <row r="72" spans="1:37" s="269" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="195"/>
-      <c r="B72" s="293">
+      <c r="B72" s="285">
         <v>2025</v>
       </c>
-      <c r="C72" s="323">
+      <c r="C72" s="315">
         <v>0.41508068721365682</v>
       </c>
       <c r="D72" s="273">
@@ -10939,22 +10920,22 @@
       <c r="N72" s="216">
         <v>0.42555365398860762</v>
       </c>
-      <c r="O72" s="311">
+      <c r="O72" s="303">
         <v>0.42911807488608505</v>
       </c>
-      <c r="P72" s="302">
+      <c r="P72" s="294">
         <f>+O72/O71-1</f>
         <v>7.3925691557103823E-2</v>
       </c>
-      <c r="Q72" s="288">
+      <c r="Q72" s="280">
         <v>0.42913526059428814</v>
       </c>
-      <c r="R72" s="302">
+      <c r="R72" s="294">
         <f>+Q72/Q71-1</f>
         <v>8.2079866784122268E-2</v>
       </c>
       <c r="S72" s="196"/>
-      <c r="T72" s="293">
+      <c r="T72" s="285">
         <v>2025</v>
       </c>
       <c r="U72" s="216">
@@ -10993,17 +10974,17 @@
       <c r="AF72" s="216">
         <v>0.42555365398860762</v>
       </c>
-      <c r="AG72" s="311">
+      <c r="AG72" s="303">
         <v>0.42372433695680284</v>
       </c>
-      <c r="AH72" s="302">
+      <c r="AH72" s="294">
         <f>+AG72/AG71-1</f>
         <v>9.961257960779113E-2</v>
       </c>
-      <c r="AI72" s="288">
+      <c r="AI72" s="280">
         <v>0.42391497681199863</v>
       </c>
-      <c r="AJ72" s="302">
+      <c r="AJ72" s="294">
         <f>+AI72/AI71-1</f>
         <v>0.10500414441849459</v>
       </c>
@@ -11011,73 +10992,73 @@
     </row>
     <row r="73" spans="1:37" s="269" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="A73" s="196"/>
-      <c r="B73" s="294">
+      <c r="B73" s="286">
         <v>2026</v>
       </c>
-      <c r="C73" s="352">
+      <c r="C73" s="343">
         <v>0.41702437628450273</v>
       </c>
-      <c r="D73" s="353">
+      <c r="D73" s="344">
         <v>0.42471543029014441</v>
       </c>
-      <c r="E73" s="353">
+      <c r="E73" s="344">
         <v>0.41705996323712052</v>
       </c>
-      <c r="F73" s="353">
+      <c r="F73" s="344">
         <v>0.4159064210552626</v>
       </c>
-      <c r="G73" s="353">
+      <c r="G73" s="344">
         <v>0.42644669416322956</v>
       </c>
-      <c r="H73" s="339">
-        <v>0.41983118844936979</v>
-      </c>
-      <c r="I73" s="339">
+      <c r="H73" s="344">
+        <v>0.41871554164804053</v>
+      </c>
+      <c r="I73" s="331">
         <v>0.41441876577248637</v>
       </c>
-      <c r="J73" s="303"/>
-      <c r="K73" s="303"/>
-      <c r="L73" s="303"/>
-      <c r="M73" s="303"/>
-      <c r="N73" s="303"/>
-      <c r="O73" s="312"/>
-      <c r="P73" s="304"/>
-      <c r="Q73" s="303"/>
-      <c r="R73" s="304"/>
+      <c r="J73" s="295"/>
+      <c r="K73" s="295"/>
+      <c r="L73" s="295"/>
+      <c r="M73" s="295"/>
+      <c r="N73" s="295"/>
+      <c r="O73" s="304"/>
+      <c r="P73" s="296"/>
+      <c r="Q73" s="295"/>
+      <c r="R73" s="296"/>
       <c r="S73" s="196"/>
-      <c r="T73" s="294">
+      <c r="T73" s="286">
         <v>2026</v>
       </c>
-      <c r="U73" s="352">
+      <c r="U73" s="343">
         <v>0.41702437628450273</v>
       </c>
-      <c r="V73" s="353">
+      <c r="V73" s="344">
         <v>0.42471543029014441</v>
       </c>
-      <c r="W73" s="353">
+      <c r="W73" s="344">
         <v>0.41705996323712052</v>
       </c>
-      <c r="X73" s="353">
+      <c r="X73" s="344">
         <v>0.4159064210552626</v>
       </c>
-      <c r="Y73" s="353">
+      <c r="Y73" s="344">
         <v>0.42644669416322956</v>
       </c>
-      <c r="Z73" s="339">
-        <v>0.41983118844936979</v>
-      </c>
-      <c r="AA73" s="339">
+      <c r="Z73" s="344">
+        <v>0.41871554164804053</v>
+      </c>
+      <c r="AA73" s="331">
         <v>0.41441876577248637</v>
       </c>
-      <c r="AB73" s="303"/>
-      <c r="AC73" s="303"/>
-      <c r="AD73" s="303"/>
-      <c r="AE73" s="303"/>
-      <c r="AF73" s="303"/>
-      <c r="AG73" s="312"/>
-      <c r="AH73" s="304"/>
-      <c r="AI73" s="303"/>
-      <c r="AJ73" s="304"/>
+      <c r="AB73" s="295"/>
+      <c r="AC73" s="295"/>
+      <c r="AD73" s="295"/>
+      <c r="AE73" s="295"/>
+      <c r="AF73" s="295"/>
+      <c r="AG73" s="304"/>
+      <c r="AH73" s="296"/>
+      <c r="AI73" s="295"/>
+      <c r="AJ73" s="296"/>
       <c r="AK73" s="198"/>
     </row>
     <row r="74" spans="1:37" ht="14.4" customHeight="1">
@@ -11095,7 +11076,7 @@
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
       <c r="L74" s="53"/>
-      <c r="M74" s="313"/>
+      <c r="M74" s="305"/>
       <c r="N74" s="7"/>
       <c r="O74" s="272"/>
       <c r="P74" s="272"/>
@@ -11115,7 +11096,7 @@
       <c r="AB74" s="7"/>
       <c r="AC74" s="7"/>
       <c r="AD74" s="53"/>
-      <c r="AE74" s="313"/>
+      <c r="AE74" s="305"/>
       <c r="AF74" s="7"/>
       <c r="AG74" s="7"/>
       <c r="AH74" s="7"/>
@@ -11367,23 +11348,23 @@
     </row>
     <row r="81" spans="1:37" ht="19.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="364"/>
-      <c r="C81" s="365"/>
-      <c r="D81" s="365"/>
-      <c r="E81" s="365"/>
-      <c r="F81" s="366"/>
-      <c r="G81" s="366"/>
-      <c r="H81" s="366"/>
-      <c r="I81" s="366"/>
-      <c r="J81" s="366"/>
-      <c r="K81" s="365"/>
-      <c r="L81" s="365"/>
-      <c r="M81" s="365"/>
-      <c r="N81" s="365"/>
-      <c r="O81" s="365"/>
-      <c r="P81" s="365"/>
-      <c r="Q81" s="365"/>
-      <c r="R81" s="365"/>
+      <c r="B81" s="355"/>
+      <c r="C81" s="356"/>
+      <c r="D81" s="356"/>
+      <c r="E81" s="356"/>
+      <c r="F81" s="357"/>
+      <c r="G81" s="357"/>
+      <c r="H81" s="357"/>
+      <c r="I81" s="357"/>
+      <c r="J81" s="357"/>
+      <c r="K81" s="356"/>
+      <c r="L81" s="356"/>
+      <c r="M81" s="356"/>
+      <c r="N81" s="356"/>
+      <c r="O81" s="356"/>
+      <c r="P81" s="356"/>
+      <c r="Q81" s="356"/>
+      <c r="R81" s="356"/>
       <c r="S81" s="7"/>
       <c r="T81" s="57"/>
       <c r="U81" s="56"/>
@@ -11410,13 +11391,13 @@
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="69"/>
-      <c r="F82" s="358" t="s">
+      <c r="F82" s="349" t="s">
         <v>26</v>
       </c>
-      <c r="G82" s="359"/>
-      <c r="H82" s="359"/>
-      <c r="I82" s="359"/>
-      <c r="J82" s="360"/>
+      <c r="G82" s="350"/>
+      <c r="H82" s="350"/>
+      <c r="I82" s="350"/>
+      <c r="J82" s="351"/>
       <c r="K82" s="70"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
@@ -13926,13 +13907,13 @@
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="69"/>
-      <c r="F10" s="367" t="s">
+      <c r="F10" s="358" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="368"/>
-      <c r="H10" s="368"/>
-      <c r="I10" s="368"/>
-      <c r="J10" s="369"/>
+      <c r="G10" s="359"/>
+      <c r="H10" s="359"/>
+      <c r="I10" s="359"/>
+      <c r="J10" s="360"/>
       <c r="K10" s="70"/>
       <c r="L10" s="12" t="s">
         <v>2</v>
@@ -13969,11 +13950,11 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="69"/>
-      <c r="G12" s="370" t="s">
+      <c r="G12" s="361" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="371"/>
-      <c r="I12" s="372"/>
+      <c r="H12" s="362"/>
+      <c r="I12" s="363"/>
       <c r="J12" s="70"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -14852,11 +14833,11 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="373" t="s">
+      <c r="G33" s="364" t="s">
         <v>44</v>
       </c>
-      <c r="H33" s="374"/>
-      <c r="I33" s="375"/>
+      <c r="H33" s="365"/>
+      <c r="I33" s="366"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -15702,8 +15683,8 @@
       <c r="L52" s="38"/>
       <c r="M52" s="76"/>
       <c r="N52" s="38"/>
-      <c r="O52" s="287"/>
-      <c r="P52" s="287"/>
+      <c r="O52" s="279"/>
+      <c r="P52" s="279"/>
       <c r="Q52" s="108"/>
     </row>
     <row r="53" spans="1:17" ht="14.4" customHeight="1">
@@ -15731,13 +15712,13 @@
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="69"/>
-      <c r="F54" s="376" t="s">
+      <c r="F54" s="367" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="377"/>
-      <c r="H54" s="377"/>
-      <c r="I54" s="377"/>
-      <c r="J54" s="377"/>
+      <c r="G54" s="368"/>
+      <c r="H54" s="368"/>
+      <c r="I54" s="368"/>
+      <c r="J54" s="368"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -16464,7 +16445,7 @@
       <c r="B70" s="200">
         <v>2025</v>
       </c>
-      <c r="C70" s="340">
+      <c r="C70" s="332">
         <v>238.3837448020885</v>
       </c>
       <c r="D70" s="274">
@@ -16526,10 +16507,10 @@
       <c r="F71" s="202">
         <v>206.50262337867446</v>
       </c>
-      <c r="G71" s="357">
-        <v>208.59964039746853</v>
-      </c>
-      <c r="H71" s="357">
+      <c r="G71" s="202">
+        <v>209.26184801947795</v>
+      </c>
+      <c r="H71" s="348">
         <v>209.81941583858563</v>
       </c>
       <c r="I71" s="202">
@@ -16855,17 +16836,17 @@
     <row r="5" spans="1:18" ht="16.2" customHeight="1" thickBot="1">
       <c r="A5" s="6"/>
       <c r="B5" s="131"/>
-      <c r="C5" s="378" t="s">
+      <c r="C5" s="369" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="379"/>
-      <c r="E5" s="379"/>
-      <c r="F5" s="379"/>
-      <c r="G5" s="379"/>
-      <c r="H5" s="379"/>
-      <c r="I5" s="379"/>
-      <c r="J5" s="379"/>
-      <c r="K5" s="380"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="370"/>
+      <c r="H5" s="370"/>
+      <c r="I5" s="370"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="371"/>
       <c r="L5" s="70"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -27548,7 +27529,7 @@
       <c r="B242" s="148">
         <v>44378</v>
       </c>
-      <c r="C242" s="347">
+      <c r="C242" s="339">
         <f t="shared" si="16"/>
         <v>15.813504263244047</v>
       </c>
@@ -27594,7 +27575,7 @@
       <c r="B243" s="148">
         <v>44409</v>
       </c>
-      <c r="C243" s="347">
+      <c r="C243" s="339">
         <f t="shared" si="16"/>
         <v>15.836401931120198</v>
       </c>
@@ -27640,7 +27621,7 @@
       <c r="B244" s="148">
         <v>44440</v>
       </c>
-      <c r="C244" s="347">
+      <c r="C244" s="339">
         <f t="shared" si="16"/>
         <v>15.656062480787583</v>
       </c>
@@ -28654,7 +28635,7 @@
       <c r="B267" s="236">
         <v>45139</v>
       </c>
-      <c r="C267" s="346">
+      <c r="C267" s="338">
         <f t="shared" si="17"/>
         <v>14.422481272119411</v>
       </c>
@@ -28700,7 +28681,7 @@
       <c r="B268" s="236">
         <v>45170</v>
       </c>
-      <c r="C268" s="346">
+      <c r="C268" s="338">
         <f t="shared" si="17"/>
         <v>14.304367760737883</v>
       </c>
@@ -28746,7 +28727,7 @@
       <c r="B269" s="236">
         <v>45200</v>
       </c>
-      <c r="C269" s="346">
+      <c r="C269" s="338">
         <f t="shared" si="17"/>
         <v>14.58323079133924</v>
       </c>
@@ -28791,7 +28772,7 @@
       <c r="B270" s="236">
         <v>45231</v>
       </c>
-      <c r="C270" s="346">
+      <c r="C270" s="338">
         <f t="shared" si="17"/>
         <v>14.402061302575852</v>
       </c>
@@ -28925,7 +28906,7 @@
       <c r="B273" s="236">
         <v>45323</v>
       </c>
-      <c r="C273" s="343">
+      <c r="C273" s="335">
         <f t="shared" si="17"/>
         <v>15.434719101666696</v>
       </c>
@@ -28972,7 +28953,7 @@
       <c r="B274" s="236">
         <v>45352</v>
       </c>
-      <c r="C274" s="343">
+      <c r="C274" s="335">
         <f t="shared" si="17"/>
         <v>16.136467771275814</v>
       </c>
@@ -29019,7 +29000,7 @@
       <c r="B275" s="236">
         <v>45383</v>
       </c>
-      <c r="C275" s="343">
+      <c r="C275" s="335">
         <f t="shared" si="17"/>
         <v>16.291173494065244</v>
       </c>
@@ -29065,7 +29046,7 @@
       <c r="B276" s="236">
         <v>45413</v>
       </c>
-      <c r="C276" s="343">
+      <c r="C276" s="335">
         <f t="shared" si="17"/>
         <v>16.307808885434902</v>
       </c>
@@ -29155,7 +29136,7 @@
       <c r="B278" s="236">
         <v>45474</v>
       </c>
-      <c r="C278" s="343">
+      <c r="C278" s="335">
         <f t="shared" si="17"/>
         <v>16.048750103626539</v>
       </c>
@@ -29201,7 +29182,7 @@
       <c r="B279" s="236">
         <v>45505</v>
       </c>
-      <c r="C279" s="343">
+      <c r="C279" s="335">
         <f t="shared" si="17"/>
         <v>16.257094942730532</v>
       </c>
@@ -29248,7 +29229,7 @@
       <c r="B280" s="236">
         <v>45536</v>
       </c>
-      <c r="C280" s="343">
+      <c r="C280" s="335">
         <f t="shared" si="17"/>
         <v>16.555598977904481</v>
       </c>
@@ -29295,7 +29276,7 @@
       <c r="B281" s="236">
         <v>45566</v>
       </c>
-      <c r="C281" s="343">
+      <c r="C281" s="335">
         <f t="shared" si="17"/>
         <v>16.268556828232569</v>
       </c>
@@ -29342,7 +29323,7 @@
       <c r="B282" s="236">
         <v>45597</v>
       </c>
-      <c r="C282" s="344">
+      <c r="C282" s="336">
         <f t="shared" si="17"/>
         <v>16.591860867115837</v>
       </c>
@@ -29389,7 +29370,7 @@
       <c r="B283" s="236">
         <v>45627</v>
       </c>
-      <c r="C283" s="344">
+      <c r="C283" s="336">
         <f t="shared" si="17"/>
         <v>17.254154066110118</v>
       </c>
@@ -29436,7 +29417,7 @@
       <c r="B284" s="226">
         <v>45658</v>
       </c>
-      <c r="C284" s="345">
+      <c r="C284" s="337">
         <f t="shared" si="17"/>
         <v>18.134875224364666</v>
       </c>
@@ -29444,7 +29425,7 @@
         <f>0.482523000428033+0.600672949706147+0.0916048031509924+0.0900744710794916</f>
         <v>1.2648752243646642</v>
       </c>
-      <c r="E284" s="285">
+      <c r="E284" s="277">
         <v>16.87</v>
       </c>
       <c r="F284" s="230">
@@ -29468,7 +29449,7 @@
         <f t="shared" si="21"/>
         <v>238.3837448020885</v>
       </c>
-      <c r="L284" s="286" t="s">
+      <c r="L284" s="278" t="s">
         <v>107</v>
       </c>
       <c r="M284" s="196"/>
@@ -29483,7 +29464,7 @@
       <c r="B285" s="236">
         <v>45689</v>
       </c>
-      <c r="C285" s="344">
+      <c r="C285" s="336">
         <f t="shared" si="17"/>
         <v>18.055108499168696</v>
       </c>
@@ -29530,7 +29511,7 @@
       <c r="B286" s="236">
         <v>45717</v>
       </c>
-      <c r="C286" s="344">
+      <c r="C286" s="336">
         <f t="shared" si="17"/>
         <v>18.381820583265164</v>
       </c>
@@ -29577,7 +29558,7 @@
       <c r="B287" s="236">
         <v>45748</v>
       </c>
-      <c r="C287" s="344">
+      <c r="C287" s="336">
         <f t="shared" si="17"/>
         <v>18.21962865654822</v>
       </c>
@@ -29624,7 +29605,7 @@
       <c r="B288" s="236">
         <v>45778</v>
       </c>
-      <c r="C288" s="344">
+      <c r="C288" s="336">
         <f t="shared" si="17"/>
         <v>17.910545122656139</v>
       </c>
@@ -29932,7 +29913,7 @@
     </row>
     <row r="295" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
       <c r="A295" s="195"/>
-      <c r="B295" s="329">
+      <c r="B295" s="321">
         <v>45992</v>
       </c>
       <c r="C295" s="251">
@@ -29942,7 +29923,7 @@
       <c r="D295" s="251">
         <v>6.7370038160060441E-3</v>
       </c>
-      <c r="E295" s="342">
+      <c r="E295" s="334">
         <v>16.66</v>
       </c>
       <c r="F295" s="253">
@@ -29966,7 +29947,7 @@
         <f t="shared" si="21"/>
         <v>220.00712402637166</v>
       </c>
-      <c r="L295" s="338"/>
+      <c r="L295" s="330"/>
       <c r="M295" s="196"/>
       <c r="N295" s="196"/>
       <c r="O295" s="197"/>
@@ -30024,7 +30005,7 @@
         <v>46054</v>
       </c>
       <c r="C297" s="225">
-        <f t="shared" ref="C297:C300" si="23">E297</f>
+        <f t="shared" ref="C297:C301" si="23">E297</f>
         <v>16.38</v>
       </c>
       <c r="D297" s="225">
@@ -30142,7 +30123,7 @@
         <f t="shared" si="21"/>
         <v>206.50262337867446</v>
       </c>
-      <c r="L299" s="356"/>
+      <c r="L299" s="347"/>
       <c r="M299" s="196"/>
       <c r="N299" s="196"/>
       <c r="O299" s="197"/>
@@ -30151,7 +30132,7 @@
       <c r="R299" s="198"/>
     </row>
     <row r="300" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A300" s="341"/>
+      <c r="A300" s="333"/>
       <c r="B300" s="236">
         <v>46143</v>
       </c>
@@ -30186,7 +30167,7 @@
         <f t="shared" si="21"/>
         <v>208.59964039746853</v>
       </c>
-      <c r="L300" s="356"/>
+      <c r="L300" s="347"/>
       <c r="M300" s="196"/>
       <c r="N300" s="196"/>
       <c r="O300" s="197"/>
@@ -30195,41 +30176,42 @@
       <c r="R300" s="198"/>
     </row>
     <row r="301" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A301" s="341"/>
-      <c r="B301" s="348">
+      <c r="A301" s="333"/>
+      <c r="B301" s="236">
         <v>46174</v>
       </c>
-      <c r="C301" s="277">
-        <v>16.904922634102324</v>
-      </c>
-      <c r="D301" s="277">
+      <c r="C301" s="225">
+        <f t="shared" si="23"/>
+        <v>16.86</v>
+      </c>
+      <c r="D301" s="225">
         <v>7.3942392978635467E-3</v>
       </c>
-      <c r="E301" s="276">
-        <v>16.904922634102324</v>
-      </c>
-      <c r="F301" s="278">
+      <c r="E301" s="249">
+        <v>16.86</v>
+      </c>
+      <c r="F301" s="203">
         <f t="shared" si="18"/>
-        <v>0.41983118844936979</v>
-      </c>
-      <c r="G301" s="279">
+        <v>0.41871554164804053</v>
+      </c>
+      <c r="G301" s="204">
         <f t="shared" si="19"/>
-        <v>0.41983118844936979</v>
-      </c>
-      <c r="H301" s="280">
+        <v>0.41871554164804053</v>
+      </c>
+      <c r="H301" s="205">
         <v>40.265999999999998</v>
       </c>
-      <c r="I301" s="281">
+      <c r="I301" s="206">
         <v>4.1255608911305482E-2</v>
       </c>
-      <c r="J301" s="282">
+      <c r="J301" s="207">
         <v>3.6966638448907747E-2</v>
       </c>
-      <c r="K301" s="283">
+      <c r="K301" s="238">
         <f t="shared" si="21"/>
-        <v>209.81941583858563</v>
-      </c>
-      <c r="L301" s="349"/>
+        <v>209.26184801947795</v>
+      </c>
+      <c r="L301" s="340"/>
       <c r="M301" s="196"/>
       <c r="N301" s="196"/>
       <c r="O301" s="197"/>
@@ -30238,38 +30220,38 @@
       <c r="R301" s="198"/>
     </row>
     <row r="302" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A302" s="341"/>
-      <c r="B302" s="350">
+      <c r="A302" s="333"/>
+      <c r="B302" s="341">
         <v>46204</v>
       </c>
-      <c r="C302" s="330">
+      <c r="C302" s="322">
         <v>16.66087764035127</v>
       </c>
-      <c r="D302" s="330">
+      <c r="D302" s="322">
         <v>7.7522292811096826E-3</v>
       </c>
-      <c r="E302" s="331">
+      <c r="E302" s="323">
         <v>16.66087764035127</v>
       </c>
-      <c r="F302" s="332">
+      <c r="F302" s="324">
         <v>0.41441876577248637</v>
       </c>
-      <c r="G302" s="333">
+      <c r="G302" s="325">
         <v>0.41441876577248637</v>
       </c>
-      <c r="H302" s="334">
+      <c r="H302" s="326">
         <v>40.203000000000003</v>
       </c>
-      <c r="I302" s="335">
+      <c r="I302" s="327">
         <v>4.0831668392197998E-2</v>
       </c>
-      <c r="J302" s="336">
+      <c r="J302" s="328">
         <v>3.6481081617249909E-2</v>
       </c>
-      <c r="K302" s="337">
+      <c r="K302" s="329">
         <v>209.22304998318674</v>
       </c>
-      <c r="L302" s="351"/>
+      <c r="L302" s="342"/>
       <c r="M302" s="196"/>
       <c r="N302" s="196"/>
       <c r="O302" s="197"/>
@@ -30278,17 +30260,17 @@
       <c r="R302" s="198"/>
     </row>
     <row r="303" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A303" s="341"/>
-      <c r="B303" s="341"/>
-      <c r="C303" s="341"/>
-      <c r="D303" s="341"/>
-      <c r="E303" s="341"/>
-      <c r="F303" s="341"/>
-      <c r="G303" s="341"/>
-      <c r="H303" s="341"/>
-      <c r="I303" s="341"/>
-      <c r="J303" s="341"/>
-      <c r="K303" s="341"/>
+      <c r="A303" s="333"/>
+      <c r="B303" s="333"/>
+      <c r="C303" s="333"/>
+      <c r="D303" s="333"/>
+      <c r="E303" s="333"/>
+      <c r="F303" s="333"/>
+      <c r="G303" s="333"/>
+      <c r="H303" s="333"/>
+      <c r="I303" s="333"/>
+      <c r="J303" s="333"/>
+      <c r="K303" s="333"/>
       <c r="L303" s="260"/>
       <c r="M303" s="196"/>
       <c r="N303" s="196"/>
@@ -30490,34 +30472,34 @@
       <c r="R312" s="129"/>
     </row>
     <row r="315" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C315" s="284"/>
+      <c r="C315" s="276"/>
     </row>
     <row r="316" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C316" s="284"/>
+      <c r="C316" s="276"/>
     </row>
     <row r="317" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C317" s="284"/>
+      <c r="C317" s="276"/>
     </row>
     <row r="318" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C318" s="284"/>
+      <c r="C318" s="276"/>
     </row>
     <row r="319" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C319" s="284"/>
+      <c r="C319" s="276"/>
     </row>
     <row r="320" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C320" s="284"/>
+      <c r="C320" s="276"/>
     </row>
     <row r="321" spans="3:3" ht="14.4" customHeight="1">
-      <c r="C321" s="284"/>
+      <c r="C321" s="276"/>
     </row>
     <row r="322" spans="3:3" ht="14.4" customHeight="1">
-      <c r="C322" s="284"/>
+      <c r="C322" s="276"/>
     </row>
     <row r="323" spans="3:3" ht="14.4" customHeight="1">
-      <c r="C323" s="284"/>
+      <c r="C323" s="276"/>
     </row>
     <row r="324" spans="3:3" ht="14.4" customHeight="1">
-      <c r="C324" s="284"/>
+      <c r="C324" s="276"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30571,26 +30553,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -30831,26 +30793,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BA7FD74-EE25-42EE-BD44-8280994753BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30867,4 +30830,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data_raw/precio_leche_productor.xlsx
+++ b/data_raw/precio_leche_productor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inaleorguy.sharepoint.com/sites/FS/Documentos compartidos/FS/Area de Información y Estudios Economicos/6.- Pagina de internet/1- Estadísticas/Uruguay/1- Producción y precios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1410" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C95AFAE-ABE1-4E9A-B758-3E547093ED10}"/>
+  <xr:revisionPtr revIDLastSave="1461" documentId="13_ncr:1_{C229F043-1FD6-4A9B-82A9-8F36A51AF250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93C52041-8D6C-4CDE-9958-955A72300432}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -452,7 +452,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="9">
+  <numFmts count="13">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
@@ -462,12 +462,23 @@
     <numFmt numFmtId="169" formatCode="General_)"/>
     <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="171" formatCode="0.0000000"/>
+    <numFmt numFmtId="175" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="182" formatCode="#,"/>
+    <numFmt numFmtId="183" formatCode="_ [$€-2]\ * #,##0.00_ ;_ [$€-2]\ * \-#,##0.00_ ;_ [$€-2]\ * &quot;-&quot;??_ "/>
+    <numFmt numFmtId="185" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -733,6 +744,25 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="1"/>
+      <color indexed="16"/>
+      <name val="Courier"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="44">
     <fill>
@@ -981,7 +1011,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="104">
+  <borders count="105">
     <border>
       <left/>
       <right/>
@@ -2184,83 +2214,155 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="62">
+  <cellStyleXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="60" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="61" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="63" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="36" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="37" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="5"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="61" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="63" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="5"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="64"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5"/>
-    <xf numFmtId="169" fontId="28" fillId="0" borderId="5"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="62" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" applyAlignment="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="64"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5"/>
+    <xf numFmtId="169" fontId="29" fillId="0" borderId="5"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="62" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" applyAlignment="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="5">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="5">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="5">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="38" fillId="40" borderId="5"/>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="5">
+    <xf numFmtId="17" fontId="39" fillId="40" borderId="5"/>
+    <xf numFmtId="0" fontId="32" fillId="39" borderId="5">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="104" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="62" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="37" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="42" fillId="0" borderId="5">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="42" fillId="0" borderId="5">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="42" fillId="0" borderId="5">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="42" fillId="0" borderId="5">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="42" fillId="0" borderId="5">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="42" fillId="0" borderId="5">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="42" fillId="0" borderId="5">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5"/>
+    <xf numFmtId="9" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="5" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="28" fillId="0" borderId="5" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="372">
+  <cellXfs count="381">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2271,11 +2373,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2286,17 +2388,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2306,10 +2408,10 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2319,9 +2421,9 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2337,7 +2439,7 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2345,20 +2447,20 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2367,7 +2469,7 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2380,8 +2482,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2391,17 +2493,17 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2413,8 +2515,8 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2425,7 +2527,7 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2435,11 +2537,11 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2451,7 +2553,7 @@
     <xf numFmtId="166" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2461,48 +2563,48 @@
     <xf numFmtId="166" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2539,13 +2641,13 @@
     <xf numFmtId="166" fontId="0" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2557,7 +2659,7 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2575,10 +2677,10 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2593,23 +2695,23 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2617,10 +2719,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2642,9 +2744,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="54" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="53" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="54" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="53" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2715,7 +2817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="55" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="55" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="41" borderId="54" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2753,10 +2855,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="5" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="5" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2783,44 +2885,44 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="95" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="96" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="97" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="98" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2839,13 +2941,13 @@
     <xf numFmtId="2" fontId="0" fillId="43" borderId="100" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2865,14 +2967,14 @@
     <xf numFmtId="2" fontId="0" fillId="7" borderId="82" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2891,59 +2993,78 @@
     <xf numFmtId="2" fontId="0" fillId="42" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="7" borderId="76" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="74" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="54" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="44" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="75" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2962,35 +3083,47 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="62">
+  <cellStyles count="109">
     <cellStyle name="20% - Énfasis1 2" xfId="11" xr:uid="{FCB0B464-9D3C-4E82-A370-39BE48DD77E0}"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="67" xr:uid="{BE5AA557-89EC-432B-81A5-0586FA49B368}"/>
     <cellStyle name="20% - Énfasis2 2" xfId="12" xr:uid="{33D245C8-3983-4F19-8721-F98BCFE18523}"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="69" xr:uid="{F5AC1844-26DD-4201-B4C8-D14569A9003C}"/>
     <cellStyle name="20% - Énfasis3 2" xfId="13" xr:uid="{1FB8FFFF-860E-4164-A95A-5321EC9FE4FB}"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="71" xr:uid="{8881F0CC-CF63-4D46-8380-9AB225684DA5}"/>
     <cellStyle name="20% - Énfasis4 2" xfId="14" xr:uid="{2EEF891A-2837-4A88-BC9E-86F7455236BD}"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="73" xr:uid="{CDD48368-A5BB-4B83-BE7B-C5B23C29F32C}"/>
     <cellStyle name="20% - Énfasis5 2" xfId="15" xr:uid="{BDFAE73B-9814-4FF2-9BB6-7FF06721A457}"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="75" xr:uid="{CCB8566D-E613-4853-A2B9-F2DDFEBA18F0}"/>
     <cellStyle name="20% - Énfasis6 2" xfId="16" xr:uid="{09E52672-73C3-4A97-A680-6A7DBC85E45A}"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="77" xr:uid="{49FD0CBF-A06C-4ED5-8D82-3E8B519CBEA6}"/>
     <cellStyle name="40% - Énfasis1 2" xfId="17" xr:uid="{F2F9643C-DE7D-4EC0-82DA-DBDD906DA828}"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="68" xr:uid="{5481D82F-30DB-4F7F-A439-A0F18CB5E87C}"/>
     <cellStyle name="40% - Énfasis2 2" xfId="18" xr:uid="{DE361482-C87A-48F3-8700-C8C9BC3B3D64}"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="70" xr:uid="{AA9E417E-7A26-43AE-8FDA-695BB37EB382}"/>
     <cellStyle name="40% - Énfasis3 2" xfId="19" xr:uid="{1DC19AD4-EFAE-4FC6-9F6F-CAA610A2BB4B}"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="72" xr:uid="{5F07693F-36C3-4779-BAA1-AA90B6890B82}"/>
     <cellStyle name="40% - Énfasis4 2" xfId="20" xr:uid="{7623447C-02FC-4321-86E3-BD188FFC9546}"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="74" xr:uid="{79A4C293-D5A9-465B-876D-C74E93FC8AB2}"/>
     <cellStyle name="40% - Énfasis5 2" xfId="21" xr:uid="{7A10FA48-BA4F-42A6-B202-6B0E4F64A50F}"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="76" xr:uid="{A819DE7E-90C2-4208-991B-67C977AC9359}"/>
     <cellStyle name="40% - Énfasis6 2" xfId="22" xr:uid="{D2467598-C938-4602-9389-F9AB7D44832F}"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="78" xr:uid="{6D059E36-D8F5-4243-AD8C-16522D88FCD6}"/>
     <cellStyle name="60% - Énfasis1 2" xfId="23" xr:uid="{538E55BC-E2C1-4A4E-8E81-C4E554988502}"/>
     <cellStyle name="60% - Énfasis2 2" xfId="24" xr:uid="{DE55BEC5-20D9-4069-9F6B-FF1466EA05A5}"/>
     <cellStyle name="60% - Énfasis3 2" xfId="25" xr:uid="{43707B36-73A8-4CD1-988A-D27585876F32}"/>
@@ -3003,6 +3136,7 @@
     <cellStyle name="Celda vinculada" xfId="7" builtinId="24" customBuiltin="1"/>
     <cellStyle name="datos principales" xfId="30" xr:uid="{4B3890D5-7161-45FA-9210-F3FF5E3367B3}"/>
     <cellStyle name="datos secundarios" xfId="31" xr:uid="{F4D583F3-7025-4E48-978B-4A34D79CDC49}"/>
+    <cellStyle name="Encabezado 1" xfId="62" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Encabezado 4 2" xfId="32" xr:uid="{FB890147-B6BD-42D9-BE5F-08010F6EC867}"/>
     <cellStyle name="Énfasis1 2" xfId="33" xr:uid="{A3882AF6-E93A-4217-80E6-2254C4442695}"/>
     <cellStyle name="Énfasis2 2" xfId="34" xr:uid="{E1CC0DAD-BCCD-4FBB-B845-00EC537B3858}"/>
@@ -3011,26 +3145,59 @@
     <cellStyle name="Énfasis5 2" xfId="37" xr:uid="{D642F439-63C9-46C7-8140-EBBEE58B0299}"/>
     <cellStyle name="Énfasis6 2" xfId="38" xr:uid="{956D6295-3A3A-442F-AE5D-731F6C867E22}"/>
     <cellStyle name="Entrada" xfId="4" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Euro" xfId="80" xr:uid="{DDAFED8B-A938-4B3E-B76C-293D4C9FC615}"/>
+    <cellStyle name="Euro 2" xfId="92" xr:uid="{33139CAB-4BD0-4871-A647-74FA5B3DCC37}"/>
+    <cellStyle name="F2" xfId="81" xr:uid="{8FBCF6A4-3B5B-4800-9D27-2DCAAB13855A}"/>
+    <cellStyle name="F3" xfId="82" xr:uid="{609A31E1-4C91-4156-9101-A1C290B483A2}"/>
+    <cellStyle name="F4" xfId="83" xr:uid="{D0748834-0116-4D03-ABDC-EC1E89DF75D2}"/>
+    <cellStyle name="F5" xfId="84" xr:uid="{72989F2B-87C8-4CFB-98E2-C893E50AEF55}"/>
+    <cellStyle name="F6" xfId="85" xr:uid="{2C3B0DE8-BE27-40BA-9CA1-9D2077EB25B5}"/>
+    <cellStyle name="F7" xfId="86" xr:uid="{6FEBF6D8-3F08-423A-AB3E-F58653800D2E}"/>
+    <cellStyle name="F8" xfId="87" xr:uid="{4F1CF34E-36B0-4785-9F46-A3C8F6465370}"/>
     <cellStyle name="Hipervínculo 2" xfId="39" xr:uid="{B541404A-0632-4BF9-A894-6EB6CF684950}"/>
     <cellStyle name="Incorrecto 2" xfId="40" xr:uid="{F809736B-1BB0-4178-91C7-F5FCC9F51133}"/>
     <cellStyle name="linea de totales" xfId="41" xr:uid="{2C7D4FD1-494E-48D0-8EB9-58B637E8CE78}"/>
     <cellStyle name="Millares 2" xfId="43" xr:uid="{A212E4C0-3074-4069-95BB-AB13BF87BB61}"/>
+    <cellStyle name="Millares 2 10" xfId="101" xr:uid="{5F0C582D-A046-4B35-8906-D2D7E35FD0C7}"/>
+    <cellStyle name="Millares 2 11" xfId="102" xr:uid="{8BEAE5E4-2047-4E86-B75E-342E3D778995}"/>
+    <cellStyle name="Millares 2 12" xfId="103" xr:uid="{088E5762-0534-4F08-8B07-97D17F7206DA}"/>
+    <cellStyle name="Millares 2 13" xfId="105" xr:uid="{000B7135-09BA-4D33-95C8-D700FEA096E5}"/>
+    <cellStyle name="Millares 2 14" xfId="106" xr:uid="{0530D907-DCB8-4D1C-B32A-D9EB0BB71A67}"/>
+    <cellStyle name="Millares 2 15" xfId="107" xr:uid="{6910A4C0-BA6F-4988-BB0F-ED40F397C129}"/>
+    <cellStyle name="Millares 2 16" xfId="108" xr:uid="{4C289B6D-BADA-4D33-AA2E-9A61605646FA}"/>
+    <cellStyle name="Millares 2 17" xfId="79" xr:uid="{8716F592-AF6E-4E95-AEC1-F65B435AEF64}"/>
+    <cellStyle name="Millares 2 2" xfId="91" xr:uid="{CBCD8CFC-2F36-4C18-9637-40ED24AF68C8}"/>
+    <cellStyle name="Millares 2 3" xfId="93" xr:uid="{EF437E0D-55DE-4E12-B595-3F247A0CBA8E}"/>
+    <cellStyle name="Millares 2 4" xfId="94" xr:uid="{6A0512C9-91F3-42B6-A21F-887240E735E1}"/>
+    <cellStyle name="Millares 2 5" xfId="95" xr:uid="{49D13F76-32FA-4964-AC6B-68B01EA6A0DF}"/>
+    <cellStyle name="Millares 2 6" xfId="96" xr:uid="{18AEB9AA-2179-40BD-A581-19C11F2C443F}"/>
+    <cellStyle name="Millares 2 7" xfId="98" xr:uid="{5CE2425B-754A-4B55-BF6D-C15EEA4DE6DC}"/>
+    <cellStyle name="Millares 2 8" xfId="99" xr:uid="{8B68983F-8A09-44C8-A983-CECC36C5FB3A}"/>
+    <cellStyle name="Millares 2 9" xfId="100" xr:uid="{AE1CCC9E-6BFC-4DE0-9F59-94ECA7F0CE42}"/>
     <cellStyle name="Millares 3" xfId="42" xr:uid="{C234FB57-7AA7-458B-B04E-92B94134C9F0}"/>
+    <cellStyle name="Millares 3 2" xfId="90" xr:uid="{40FC5269-CAEB-4FEB-8713-E5E8E69AB3A2}"/>
+    <cellStyle name="Millares 4" xfId="64" xr:uid="{587A4DE2-30F3-4167-8777-5D808B7F6EB5}"/>
     <cellStyle name="Neutral 2" xfId="44" xr:uid="{8B96D84A-9BCE-4A11-8D55-F143D6B1E8A2}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 11" xfId="45" xr:uid="{487AB470-19A6-4D20-B097-47B56DDDBE62}"/>
     <cellStyle name="Normal 13" xfId="46" xr:uid="{33A061A9-4027-4ECC-8FF7-405655B776F9}"/>
     <cellStyle name="Normal 14" xfId="47" xr:uid="{9A389838-6683-4F97-A100-0A0600DE8A6D}"/>
     <cellStyle name="Normal 2" xfId="48" xr:uid="{E818DC2C-EE93-40E6-809B-E913D6907D53}"/>
+    <cellStyle name="Normal 2 2" xfId="88" xr:uid="{5B1D174F-87CA-496E-9CD4-364319EAB235}"/>
     <cellStyle name="Normal 3" xfId="49" xr:uid="{CC5B07E7-62BE-48AE-82B8-D6343196CF7D}"/>
     <cellStyle name="Normal 4" xfId="50" xr:uid="{C879FD48-EBDD-4B04-9E7B-3F61905FF102}"/>
     <cellStyle name="Normal 5" xfId="10" xr:uid="{BFDD987D-32B7-4566-9921-8032B8ADB20C}"/>
+    <cellStyle name="Normal 6" xfId="63" xr:uid="{BB7E1154-4F49-4AC9-93C6-D95624D793E6}"/>
     <cellStyle name="Notas 2" xfId="51" xr:uid="{26319967-3D8C-4E9E-859E-CEEF2C6A36A2}"/>
+    <cellStyle name="Notas 3" xfId="66" xr:uid="{B96506B1-8C1D-42EA-B06C-5E40921A7714}"/>
     <cellStyle name="Notas al pie" xfId="52" xr:uid="{489F72AB-4EFA-400A-8D44-304E9D219C97}"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
     <cellStyle name="Porcentaje 2" xfId="53" xr:uid="{D150DC80-8DEC-48C5-B64E-88B4664C769B}"/>
+    <cellStyle name="Porcentaje 3" xfId="65" xr:uid="{65F7667E-D892-456F-BA0B-12358F6B0604}"/>
+    <cellStyle name="Porcentual 2" xfId="89" xr:uid="{47497BE6-1258-499D-9C11-7E2975A80F65}"/>
     <cellStyle name="Porcentual 3" xfId="54" xr:uid="{7728F4AB-FF99-46F1-9659-4EFB7FCAEBC3}"/>
     <cellStyle name="Salida" xfId="5" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Standard 10" xfId="97" xr:uid="{8329947A-1E63-47FF-A4B0-ED64858F263E}"/>
     <cellStyle name="subtitulos de las filas" xfId="55" xr:uid="{B490BF38-106F-4219-8479-6AF71053632C}"/>
     <cellStyle name="Texto de advertencia 2" xfId="56" xr:uid="{95D7AC1F-F749-4D6F-8133-27E5CDFBA9F9}"/>
     <cellStyle name="Texto explicativo 2" xfId="57" xr:uid="{0DEBA02D-B57C-44EA-9CBE-9747277C30AB}"/>
@@ -3041,6 +3208,7 @@
     <cellStyle name="titulos de las columnas" xfId="60" xr:uid="{2DB2F740-6C7C-47C0-A4CB-6F91FD5665AB}"/>
     <cellStyle name="titulos de las filas" xfId="61" xr:uid="{86694EA2-A522-4E1A-9FEC-BFFC84A526BC}"/>
     <cellStyle name="Total" xfId="9" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="WinCalendar_BlankDates_12" xfId="104" xr:uid="{0EA9D97D-C32E-4C86-AC87-EC29DAFCCC55}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -4800,17 +4968,17 @@
       <c r="B10" s="14"/>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
-      <c r="E10" s="352" t="s">
+      <c r="E10" s="361" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="353"/>
-      <c r="G10" s="353"/>
-      <c r="H10" s="353"/>
-      <c r="I10" s="353"/>
-      <c r="J10" s="353"/>
-      <c r="K10" s="353"/>
-      <c r="L10" s="353"/>
-      <c r="M10" s="354"/>
+      <c r="F10" s="362"/>
+      <c r="G10" s="362"/>
+      <c r="H10" s="362"/>
+      <c r="I10" s="362"/>
+      <c r="J10" s="362"/>
+      <c r="K10" s="362"/>
+      <c r="L10" s="362"/>
+      <c r="M10" s="363"/>
       <c r="N10" s="17"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -4820,17 +4988,17 @@
       <c r="T10" s="19"/>
       <c r="U10" s="15"/>
       <c r="V10" s="16"/>
-      <c r="W10" s="349" t="s">
+      <c r="W10" s="358" t="s">
         <v>3</v>
       </c>
-      <c r="X10" s="350"/>
-      <c r="Y10" s="350"/>
-      <c r="Z10" s="350"/>
-      <c r="AA10" s="350"/>
-      <c r="AB10" s="350"/>
-      <c r="AC10" s="350"/>
-      <c r="AD10" s="350"/>
-      <c r="AE10" s="351"/>
+      <c r="X10" s="359"/>
+      <c r="Y10" s="359"/>
+      <c r="Z10" s="359"/>
+      <c r="AA10" s="359"/>
+      <c r="AB10" s="359"/>
+      <c r="AC10" s="359"/>
+      <c r="AD10" s="359"/>
+      <c r="AE10" s="360"/>
       <c r="AF10" s="17"/>
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
@@ -7735,8 +7903,12 @@
       <c r="I37" s="331">
         <v>16.66087764035127</v>
       </c>
-      <c r="J37" s="295"/>
-      <c r="K37" s="295"/>
+      <c r="J37" s="331">
+        <v>16.456067759585004</v>
+      </c>
+      <c r="K37" s="331">
+        <v>16.47896718396818</v>
+      </c>
       <c r="L37" s="295"/>
       <c r="M37" s="295"/>
       <c r="N37" s="295"/>
@@ -7769,8 +7941,12 @@
       <c r="AA37" s="331">
         <v>16.66087764035127</v>
       </c>
-      <c r="AB37" s="295"/>
-      <c r="AC37" s="295"/>
+      <c r="AB37" s="331">
+        <v>16.456067759585004</v>
+      </c>
+      <c r="AC37" s="331">
+        <v>16.47896718396818</v>
+      </c>
       <c r="AD37" s="295"/>
       <c r="AE37" s="295"/>
       <c r="AF37" s="295"/>
@@ -8066,23 +8242,23 @@
     </row>
     <row r="45" spans="1:37" ht="36" customHeight="1">
       <c r="A45" s="68"/>
-      <c r="B45" s="355"/>
-      <c r="C45" s="356"/>
-      <c r="D45" s="356"/>
-      <c r="E45" s="357"/>
-      <c r="F45" s="357"/>
-      <c r="G45" s="357"/>
-      <c r="H45" s="357"/>
-      <c r="I45" s="357"/>
-      <c r="J45" s="357"/>
-      <c r="K45" s="357"/>
-      <c r="L45" s="357"/>
-      <c r="M45" s="357"/>
-      <c r="N45" s="356"/>
-      <c r="O45" s="356"/>
-      <c r="P45" s="356"/>
-      <c r="Q45" s="356"/>
-      <c r="R45" s="356"/>
+      <c r="B45" s="364"/>
+      <c r="C45" s="365"/>
+      <c r="D45" s="365"/>
+      <c r="E45" s="366"/>
+      <c r="F45" s="366"/>
+      <c r="G45" s="366"/>
+      <c r="H45" s="366"/>
+      <c r="I45" s="366"/>
+      <c r="J45" s="366"/>
+      <c r="K45" s="366"/>
+      <c r="L45" s="366"/>
+      <c r="M45" s="366"/>
+      <c r="N45" s="365"/>
+      <c r="O45" s="365"/>
+      <c r="P45" s="365"/>
+      <c r="Q45" s="365"/>
+      <c r="R45" s="365"/>
       <c r="S45" s="7"/>
       <c r="T45" s="8"/>
       <c r="U45" s="7"/>
@@ -8108,17 +8284,17 @@
       <c r="B46" s="11"/>
       <c r="C46" s="7"/>
       <c r="D46" s="69"/>
-      <c r="E46" s="352" t="s">
+      <c r="E46" s="361" t="s">
         <v>97</v>
       </c>
-      <c r="F46" s="353"/>
-      <c r="G46" s="353"/>
-      <c r="H46" s="353"/>
-      <c r="I46" s="353"/>
-      <c r="J46" s="353"/>
-      <c r="K46" s="353"/>
-      <c r="L46" s="353"/>
-      <c r="M46" s="354"/>
+      <c r="F46" s="362"/>
+      <c r="G46" s="362"/>
+      <c r="H46" s="362"/>
+      <c r="I46" s="362"/>
+      <c r="J46" s="362"/>
+      <c r="K46" s="362"/>
+      <c r="L46" s="362"/>
+      <c r="M46" s="363"/>
       <c r="N46" s="70"/>
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
@@ -8128,17 +8304,17 @@
       <c r="T46" s="71"/>
       <c r="U46" s="7"/>
       <c r="V46" s="69"/>
-      <c r="W46" s="349" t="s">
+      <c r="W46" s="358" t="s">
         <v>25</v>
       </c>
-      <c r="X46" s="350"/>
-      <c r="Y46" s="350"/>
-      <c r="Z46" s="350"/>
-      <c r="AA46" s="350"/>
-      <c r="AB46" s="350"/>
-      <c r="AC46" s="350"/>
-      <c r="AD46" s="350"/>
-      <c r="AE46" s="351"/>
+      <c r="X46" s="359"/>
+      <c r="Y46" s="359"/>
+      <c r="Z46" s="359"/>
+      <c r="AA46" s="359"/>
+      <c r="AB46" s="359"/>
+      <c r="AC46" s="359"/>
+      <c r="AD46" s="359"/>
+      <c r="AE46" s="360"/>
       <c r="AF46" s="70"/>
       <c r="AG46" s="7"/>
       <c r="AH46" s="7"/>
@@ -11016,8 +11192,12 @@
       <c r="I73" s="331">
         <v>0.41441876577248637</v>
       </c>
-      <c r="J73" s="295"/>
-      <c r="K73" s="295"/>
+      <c r="J73" s="331">
+        <v>0.40932437279767686</v>
+      </c>
+      <c r="K73" s="331">
+        <v>0.4098531893443475</v>
+      </c>
       <c r="L73" s="295"/>
       <c r="M73" s="295"/>
       <c r="N73" s="295"/>
@@ -11050,8 +11230,12 @@
       <c r="AA73" s="331">
         <v>0.41441876577248637</v>
       </c>
-      <c r="AB73" s="295"/>
-      <c r="AC73" s="295"/>
+      <c r="AB73" s="331">
+        <v>0.40932437279767686</v>
+      </c>
+      <c r="AC73" s="331">
+        <v>0.4098531893443475</v>
+      </c>
       <c r="AD73" s="295"/>
       <c r="AE73" s="295"/>
       <c r="AF73" s="295"/>
@@ -11348,23 +11532,23 @@
     </row>
     <row r="81" spans="1:37" ht="19.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="355"/>
-      <c r="C81" s="356"/>
-      <c r="D81" s="356"/>
-      <c r="E81" s="356"/>
-      <c r="F81" s="357"/>
-      <c r="G81" s="357"/>
-      <c r="H81" s="357"/>
-      <c r="I81" s="357"/>
-      <c r="J81" s="357"/>
-      <c r="K81" s="356"/>
-      <c r="L81" s="356"/>
-      <c r="M81" s="356"/>
-      <c r="N81" s="356"/>
-      <c r="O81" s="356"/>
-      <c r="P81" s="356"/>
-      <c r="Q81" s="356"/>
-      <c r="R81" s="356"/>
+      <c r="B81" s="364"/>
+      <c r="C81" s="365"/>
+      <c r="D81" s="365"/>
+      <c r="E81" s="365"/>
+      <c r="F81" s="366"/>
+      <c r="G81" s="366"/>
+      <c r="H81" s="366"/>
+      <c r="I81" s="366"/>
+      <c r="J81" s="366"/>
+      <c r="K81" s="365"/>
+      <c r="L81" s="365"/>
+      <c r="M81" s="365"/>
+      <c r="N81" s="365"/>
+      <c r="O81" s="365"/>
+      <c r="P81" s="365"/>
+      <c r="Q81" s="365"/>
+      <c r="R81" s="365"/>
       <c r="S81" s="7"/>
       <c r="T81" s="57"/>
       <c r="U81" s="56"/>
@@ -11391,13 +11575,13 @@
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="69"/>
-      <c r="F82" s="349" t="s">
+      <c r="F82" s="358" t="s">
         <v>26</v>
       </c>
-      <c r="G82" s="350"/>
-      <c r="H82" s="350"/>
-      <c r="I82" s="350"/>
-      <c r="J82" s="351"/>
+      <c r="G82" s="359"/>
+      <c r="H82" s="359"/>
+      <c r="I82" s="359"/>
+      <c r="J82" s="360"/>
       <c r="K82" s="70"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
@@ -13261,8 +13445,12 @@
       <c r="I109" s="46">
         <v>40.203000000000003</v>
       </c>
-      <c r="J109" s="46"/>
-      <c r="K109" s="46"/>
+      <c r="J109" s="46">
+        <v>40.203000000000003</v>
+      </c>
+      <c r="K109" s="46">
+        <v>40.207000000000001</v>
+      </c>
       <c r="L109" s="46"/>
       <c r="M109" s="46"/>
       <c r="N109" s="47"/>
@@ -13907,13 +14095,13 @@
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="69"/>
-      <c r="F10" s="358" t="s">
+      <c r="F10" s="367" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="359"/>
-      <c r="H10" s="359"/>
-      <c r="I10" s="359"/>
-      <c r="J10" s="360"/>
+      <c r="G10" s="368"/>
+      <c r="H10" s="368"/>
+      <c r="I10" s="368"/>
+      <c r="J10" s="369"/>
       <c r="K10" s="70"/>
       <c r="L10" s="12" t="s">
         <v>2</v>
@@ -13950,11 +14138,11 @@
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="69"/>
-      <c r="G12" s="361" t="s">
+      <c r="G12" s="370" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="362"/>
-      <c r="I12" s="363"/>
+      <c r="H12" s="371"/>
+      <c r="I12" s="372"/>
       <c r="J12" s="70"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -14755,8 +14943,12 @@
       <c r="I29" s="104">
         <v>4.0831668392197998E-2</v>
       </c>
-      <c r="J29" s="104"/>
-      <c r="K29" s="104"/>
+      <c r="J29" s="104">
+        <v>4.0358494253814485E-2</v>
+      </c>
+      <c r="K29" s="104">
+        <v>3.9471154251157388E-2</v>
+      </c>
       <c r="L29" s="104"/>
       <c r="M29" s="104"/>
       <c r="N29" s="105"/>
@@ -14833,11 +15025,11 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="364" t="s">
+      <c r="G33" s="373" t="s">
         <v>44</v>
       </c>
-      <c r="H33" s="365"/>
-      <c r="I33" s="366"/>
+      <c r="H33" s="374"/>
+      <c r="I33" s="375"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -15636,8 +15828,12 @@
       <c r="I50" s="104">
         <v>3.6481081617249909E-2</v>
       </c>
-      <c r="J50" s="104"/>
-      <c r="K50" s="104"/>
+      <c r="J50" s="104">
+        <v>3.6184912999646879E-2</v>
+      </c>
+      <c r="K50" s="104">
+        <v>3.6590142813031606E-2</v>
+      </c>
       <c r="L50" s="104"/>
       <c r="M50" s="104"/>
       <c r="N50" s="105"/>
@@ -15712,13 +15908,13 @@
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="69"/>
-      <c r="F54" s="367" t="s">
+      <c r="F54" s="376" t="s">
         <v>45</v>
       </c>
-      <c r="G54" s="368"/>
-      <c r="H54" s="368"/>
-      <c r="I54" s="368"/>
-      <c r="J54" s="368"/>
+      <c r="G54" s="377"/>
+      <c r="H54" s="377"/>
+      <c r="I54" s="377"/>
+      <c r="J54" s="377"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -16508,16 +16704,20 @@
         <v>206.50262337867446</v>
       </c>
       <c r="G71" s="202">
+        <v>208.59964039746853</v>
+      </c>
+      <c r="H71" s="202">
         <v>209.26184801947795</v>
       </c>
-      <c r="H71" s="348">
-        <v>209.81941583858563</v>
-      </c>
-      <c r="I71" s="202">
-        <v>209.22304998318674</v>
-      </c>
-      <c r="J71" s="202"/>
-      <c r="K71" s="202"/>
+      <c r="I71" s="348">
+        <v>209.22304998318677</v>
+      </c>
+      <c r="J71" s="348">
+        <v>208.72816338351055</v>
+      </c>
+      <c r="K71" s="348">
+        <v>210.34347143050678</v>
+      </c>
       <c r="L71" s="202"/>
       <c r="M71" s="202"/>
       <c r="N71" s="202"/>
@@ -16713,7 +16913,7 @@
     <mergeCell ref="G33:I33"/>
     <mergeCell ref="F54:J54"/>
   </mergeCells>
-  <phoneticPr fontId="39" type="noConversion"/>
+  <phoneticPr fontId="40" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="L10" location="'Listado Datos'!R1C1" display="Acceder al listado de datos" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
@@ -16732,7 +16932,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R324"/>
+  <dimension ref="A1:R326"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" customWidth="1"/>
@@ -16836,17 +17036,17 @@
     <row r="5" spans="1:18" ht="16.2" customHeight="1" thickBot="1">
       <c r="A5" s="6"/>
       <c r="B5" s="131"/>
-      <c r="C5" s="369" t="s">
+      <c r="C5" s="378" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="370"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="370"/>
-      <c r="I5" s="370"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="371"/>
+      <c r="D5" s="379"/>
+      <c r="E5" s="379"/>
+      <c r="F5" s="379"/>
+      <c r="G5" s="379"/>
+      <c r="H5" s="379"/>
+      <c r="I5" s="379"/>
+      <c r="J5" s="379"/>
+      <c r="K5" s="380"/>
       <c r="L5" s="70"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -28518,7 +28718,7 @@
         <v>0.45315354725817658</v>
       </c>
       <c r="G264" s="204">
-        <f t="shared" ref="G264:G301" si="19">E264/H264</f>
+        <f t="shared" ref="G264:G303" si="19">E264/H264</f>
         <v>0.45315354725817658</v>
       </c>
       <c r="H264" s="205">
@@ -28800,7 +29000,7 @@
         <v>3.4547912831612973E-2</v>
       </c>
       <c r="K270" s="238">
-        <f t="shared" ref="K270:K301" si="21">C270/1.03/(I270+J270)</f>
+        <f t="shared" ref="K270:K304" si="21">C270/1.03/(I270+J270)</f>
         <v>192.128050061945</v>
       </c>
       <c r="L270" s="241" t="s">
@@ -30176,7 +30376,7 @@
       <c r="R300" s="198"/>
     </row>
     <row r="301" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A301" s="333"/>
+      <c r="A301" s="195"/>
       <c r="B301" s="236">
         <v>46174</v>
       </c>
@@ -30211,7 +30411,7 @@
         <f t="shared" si="21"/>
         <v>209.26184801947795</v>
       </c>
-      <c r="L301" s="340"/>
+      <c r="L301" s="263"/>
       <c r="M301" s="196"/>
       <c r="N301" s="196"/>
       <c r="O301" s="197"/>
@@ -30221,37 +30421,39 @@
     </row>
     <row r="302" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
       <c r="A302" s="333"/>
-      <c r="B302" s="341">
+      <c r="B302" s="350">
         <v>46204</v>
       </c>
-      <c r="C302" s="322">
+      <c r="C302" s="351">
         <v>16.66087764035127</v>
       </c>
-      <c r="D302" s="322">
+      <c r="D302" s="351">
         <v>7.7522292811096826E-3</v>
       </c>
-      <c r="E302" s="323">
+      <c r="E302" s="349">
         <v>16.66087764035127</v>
       </c>
-      <c r="F302" s="324">
+      <c r="F302" s="352">
         <v>0.41441876577248637</v>
       </c>
-      <c r="G302" s="325">
+      <c r="G302" s="353">
+        <f t="shared" si="19"/>
         <v>0.41441876577248637</v>
       </c>
-      <c r="H302" s="326">
+      <c r="H302" s="354">
         <v>40.203000000000003</v>
       </c>
-      <c r="I302" s="327">
+      <c r="I302" s="355">
         <v>4.0831668392197998E-2</v>
       </c>
-      <c r="J302" s="328">
+      <c r="J302" s="356">
         <v>3.6481081617249909E-2</v>
       </c>
-      <c r="K302" s="329">
-        <v>209.22304998318674</v>
-      </c>
-      <c r="L302" s="342"/>
+      <c r="K302" s="357">
+        <f t="shared" si="21"/>
+        <v>209.22304998318677</v>
+      </c>
+      <c r="L302" s="340"/>
       <c r="M302" s="196"/>
       <c r="N302" s="196"/>
       <c r="O302" s="197"/>
@@ -30261,17 +30463,39 @@
     </row>
     <row r="303" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
       <c r="A303" s="333"/>
-      <c r="B303" s="333"/>
-      <c r="C303" s="333"/>
-      <c r="D303" s="333"/>
-      <c r="E303" s="333"/>
-      <c r="F303" s="333"/>
-      <c r="G303" s="333"/>
-      <c r="H303" s="333"/>
-      <c r="I303" s="333"/>
-      <c r="J303" s="333"/>
-      <c r="K303" s="333"/>
-      <c r="L303" s="260"/>
+      <c r="B303" s="350">
+        <v>46235</v>
+      </c>
+      <c r="C303" s="351">
+        <v>16.456067759585004</v>
+      </c>
+      <c r="D303" s="351">
+        <v>7.2332668187425836E-3</v>
+      </c>
+      <c r="E303" s="349">
+        <v>16.456067759585004</v>
+      </c>
+      <c r="F303" s="352">
+        <v>0.40932437279767686</v>
+      </c>
+      <c r="G303" s="353">
+        <f t="shared" si="19"/>
+        <v>0.40932437279767686</v>
+      </c>
+      <c r="H303" s="354">
+        <v>40.203000000000003</v>
+      </c>
+      <c r="I303" s="355">
+        <v>4.0358494253814485E-2</v>
+      </c>
+      <c r="J303" s="356">
+        <v>3.6184912999646879E-2</v>
+      </c>
+      <c r="K303" s="357">
+        <f t="shared" si="21"/>
+        <v>208.72816338351055</v>
+      </c>
+      <c r="L303" s="340"/>
       <c r="M303" s="196"/>
       <c r="N303" s="196"/>
       <c r="O303" s="197"/>
@@ -30279,54 +30503,71 @@
       <c r="Q303" s="196"/>
       <c r="R303" s="198"/>
     </row>
-    <row r="304" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A304" s="6"/>
-      <c r="B304" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C304" s="15"/>
-      <c r="D304" s="15"/>
-      <c r="E304" s="189"/>
-      <c r="F304" s="15"/>
-      <c r="G304" s="15"/>
-      <c r="H304" s="15"/>
-      <c r="I304" s="15"/>
-      <c r="J304" s="15"/>
-      <c r="K304" s="15"/>
-      <c r="L304" s="15"/>
-      <c r="M304" s="15"/>
-      <c r="N304" s="15"/>
-      <c r="O304" s="18"/>
-      <c r="P304" s="7"/>
-      <c r="Q304" s="7"/>
-      <c r="R304" s="90"/>
-    </row>
-    <row r="305" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A305" s="6"/>
-      <c r="B305" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C305" s="15"/>
-      <c r="D305" s="15"/>
-      <c r="E305" s="189"/>
-      <c r="F305" s="15"/>
-      <c r="G305" s="15"/>
-      <c r="H305" s="15"/>
-      <c r="I305" s="15"/>
-      <c r="J305" s="15"/>
-      <c r="K305" s="15"/>
-      <c r="L305" s="15"/>
-      <c r="M305" s="15"/>
-      <c r="N305" s="15"/>
-      <c r="O305" s="18"/>
-      <c r="P305" s="7"/>
-      <c r="Q305" s="7"/>
-      <c r="R305" s="90"/>
+    <row r="304" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A304" s="333"/>
+      <c r="B304" s="341">
+        <v>46266</v>
+      </c>
+      <c r="C304" s="322">
+        <v>16.47896718396818</v>
+      </c>
+      <c r="D304" s="322">
+        <v>8.1233733232211058E-3</v>
+      </c>
+      <c r="E304" s="323">
+        <v>16.47896718396818</v>
+      </c>
+      <c r="F304" s="324">
+        <v>0.4098531893443475</v>
+      </c>
+      <c r="G304" s="325">
+        <v>0.4098531893443475</v>
+      </c>
+      <c r="H304" s="326">
+        <v>40.207000000000001</v>
+      </c>
+      <c r="I304" s="327">
+        <v>3.9471154251157388E-2</v>
+      </c>
+      <c r="J304" s="328">
+        <v>3.6590142813031606E-2</v>
+      </c>
+      <c r="K304" s="329">
+        <f t="shared" si="21"/>
+        <v>210.34347143050678</v>
+      </c>
+      <c r="L304" s="342"/>
+      <c r="M304" s="196"/>
+      <c r="N304" s="196"/>
+      <c r="O304" s="197"/>
+      <c r="P304" s="196"/>
+      <c r="Q304" s="196"/>
+      <c r="R304" s="198"/>
+    </row>
+    <row r="305" spans="1:18" s="199" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A305" s="333"/>
+      <c r="B305" s="333"/>
+      <c r="C305" s="333"/>
+      <c r="D305" s="333"/>
+      <c r="E305" s="333"/>
+      <c r="F305" s="333"/>
+      <c r="G305" s="333"/>
+      <c r="H305" s="333"/>
+      <c r="I305" s="333"/>
+      <c r="J305" s="333"/>
+      <c r="K305" s="333"/>
+      <c r="L305" s="260"/>
+      <c r="M305" s="196"/>
+      <c r="N305" s="196"/>
+      <c r="O305" s="197"/>
+      <c r="P305" s="196"/>
+      <c r="Q305" s="196"/>
+      <c r="R305" s="198"/>
     </row>
     <row r="306" spans="1:18" ht="14.4" customHeight="1">
       <c r="A306" s="6"/>
-      <c r="B306" s="14" t="s">
-        <v>96</v>
+      <c r="B306" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="C306" s="15"/>
       <c r="D306" s="15"/>
@@ -30347,7 +30588,9 @@
     </row>
     <row r="307" spans="1:18" ht="14.4" customHeight="1">
       <c r="A307" s="6"/>
-      <c r="B307" s="190"/>
+      <c r="B307" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="C307" s="15"/>
       <c r="D307" s="15"/>
       <c r="E307" s="189"/>
@@ -30358,124 +30601,160 @@
       <c r="J307" s="15"/>
       <c r="K307" s="15"/>
       <c r="L307" s="15"/>
-      <c r="M307" s="7"/>
-      <c r="N307" s="7"/>
+      <c r="M307" s="15"/>
+      <c r="N307" s="15"/>
       <c r="O307" s="18"/>
       <c r="P307" s="7"/>
       <c r="Q307" s="7"/>
       <c r="R307" s="90"/>
     </row>
-    <row r="308" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A308" s="49"/>
-      <c r="B308" s="124"/>
-      <c r="C308" s="63" t="s">
+    <row r="308" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A308" s="6"/>
+      <c r="B308" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C308" s="15"/>
+      <c r="D308" s="15"/>
+      <c r="E308" s="189"/>
+      <c r="F308" s="15"/>
+      <c r="G308" s="15"/>
+      <c r="H308" s="15"/>
+      <c r="I308" s="15"/>
+      <c r="J308" s="15"/>
+      <c r="K308" s="15"/>
+      <c r="L308" s="15"/>
+      <c r="M308" s="15"/>
+      <c r="N308" s="15"/>
+      <c r="O308" s="18"/>
+      <c r="P308" s="7"/>
+      <c r="Q308" s="7"/>
+      <c r="R308" s="90"/>
+    </row>
+    <row r="309" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A309" s="6"/>
+      <c r="B309" s="190"/>
+      <c r="C309" s="15"/>
+      <c r="D309" s="15"/>
+      <c r="E309" s="189"/>
+      <c r="F309" s="15"/>
+      <c r="G309" s="15"/>
+      <c r="H309" s="15"/>
+      <c r="I309" s="15"/>
+      <c r="J309" s="15"/>
+      <c r="K309" s="15"/>
+      <c r="L309" s="15"/>
+      <c r="M309" s="7"/>
+      <c r="N309" s="7"/>
+      <c r="O309" s="18"/>
+      <c r="P309" s="7"/>
+      <c r="Q309" s="7"/>
+      <c r="R309" s="90"/>
+    </row>
+    <row r="310" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A310" s="49"/>
+      <c r="B310" s="124"/>
+      <c r="C310" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="D308" s="56"/>
-      <c r="E308" s="189"/>
-      <c r="F308" s="56"/>
-      <c r="G308" s="56"/>
-      <c r="H308" s="56"/>
-      <c r="I308" s="56"/>
-      <c r="J308" s="56"/>
-      <c r="K308" s="56"/>
-      <c r="L308" s="56"/>
-      <c r="M308" s="56"/>
-      <c r="N308" s="56"/>
-      <c r="O308" s="56"/>
-      <c r="P308" s="56"/>
-      <c r="Q308" s="56"/>
-      <c r="R308" s="191"/>
-    </row>
-    <row r="309" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A309" s="49"/>
-      <c r="B309" s="125"/>
-      <c r="C309" s="63" t="s">
+      <c r="D310" s="56"/>
+      <c r="E310" s="189"/>
+      <c r="F310" s="56"/>
+      <c r="G310" s="56"/>
+      <c r="H310" s="56"/>
+      <c r="I310" s="56"/>
+      <c r="J310" s="56"/>
+      <c r="K310" s="56"/>
+      <c r="L310" s="56"/>
+      <c r="M310" s="56"/>
+      <c r="N310" s="56"/>
+      <c r="O310" s="56"/>
+      <c r="P310" s="56"/>
+      <c r="Q310" s="56"/>
+      <c r="R310" s="191"/>
+    </row>
+    <row r="311" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A311" s="49"/>
+      <c r="B311" s="125"/>
+      <c r="C311" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D309" s="56"/>
-      <c r="E309" s="189"/>
-      <c r="F309" s="56"/>
-      <c r="G309" s="56"/>
-      <c r="H309" s="56"/>
-      <c r="I309" s="56"/>
-      <c r="J309" s="56"/>
-      <c r="K309" s="56"/>
-      <c r="L309" s="56"/>
-      <c r="M309" s="56"/>
-      <c r="N309" s="65"/>
-      <c r="O309" s="7"/>
-      <c r="P309" s="56"/>
-      <c r="Q309" s="56"/>
-      <c r="R309" s="191"/>
-    </row>
-    <row r="310" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A310" s="6"/>
-      <c r="B310" s="62"/>
-      <c r="C310" s="63" t="s">
+      <c r="D311" s="56"/>
+      <c r="E311" s="189"/>
+      <c r="F311" s="56"/>
+      <c r="G311" s="56"/>
+      <c r="H311" s="56"/>
+      <c r="I311" s="56"/>
+      <c r="J311" s="56"/>
+      <c r="K311" s="56"/>
+      <c r="L311" s="56"/>
+      <c r="M311" s="56"/>
+      <c r="N311" s="65"/>
+      <c r="O311" s="7"/>
+      <c r="P311" s="56"/>
+      <c r="Q311" s="56"/>
+      <c r="R311" s="191"/>
+    </row>
+    <row r="312" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A312" s="6"/>
+      <c r="B312" s="62"/>
+      <c r="C312" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D310" s="56"/>
-      <c r="E310" s="56"/>
-      <c r="F310" s="192"/>
-      <c r="G310" s="7"/>
-      <c r="H310" s="192"/>
-      <c r="I310" s="192"/>
-      <c r="J310" s="192"/>
-      <c r="K310" s="192"/>
-      <c r="L310" s="7"/>
-      <c r="M310" s="7"/>
-      <c r="N310" s="7"/>
-      <c r="O310" s="7"/>
-      <c r="P310" s="7"/>
-      <c r="Q310" s="7"/>
-      <c r="R310" s="90"/>
-    </row>
-    <row r="311" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A311" s="6"/>
-      <c r="B311" s="7"/>
-      <c r="C311" s="192"/>
-      <c r="D311" s="7"/>
-      <c r="E311" s="189"/>
-      <c r="F311" s="192"/>
-      <c r="G311" s="7"/>
-      <c r="H311" s="192"/>
-      <c r="I311" s="192"/>
-      <c r="J311" s="192"/>
-      <c r="K311" s="192"/>
-      <c r="L311" s="7"/>
-      <c r="M311" s="7"/>
-      <c r="N311" s="7"/>
-      <c r="O311" s="7"/>
-      <c r="P311" s="7"/>
-      <c r="Q311" s="7"/>
-      <c r="R311" s="90"/>
-    </row>
-    <row r="312" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A312" s="85"/>
-      <c r="B312" s="86"/>
-      <c r="C312" s="193"/>
-      <c r="D312" s="86"/>
-      <c r="E312" s="86"/>
-      <c r="F312" s="193"/>
-      <c r="G312" s="86"/>
-      <c r="H312" s="193"/>
-      <c r="I312" s="193"/>
-      <c r="J312" s="193"/>
-      <c r="K312" s="193"/>
-      <c r="L312" s="86"/>
-      <c r="M312" s="86"/>
-      <c r="N312" s="86"/>
-      <c r="O312" s="86"/>
-      <c r="P312" s="86"/>
-      <c r="Q312" s="86"/>
-      <c r="R312" s="129"/>
-    </row>
-    <row r="315" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C315" s="276"/>
-    </row>
-    <row r="316" spans="1:18" ht="14.4" customHeight="1">
-      <c r="C316" s="276"/>
+      <c r="D312" s="56"/>
+      <c r="E312" s="56"/>
+      <c r="F312" s="192"/>
+      <c r="G312" s="7"/>
+      <c r="H312" s="192"/>
+      <c r="I312" s="192"/>
+      <c r="J312" s="192"/>
+      <c r="K312" s="192"/>
+      <c r="L312" s="7"/>
+      <c r="M312" s="7"/>
+      <c r="N312" s="7"/>
+      <c r="O312" s="7"/>
+      <c r="P312" s="7"/>
+      <c r="Q312" s="7"/>
+      <c r="R312" s="90"/>
+    </row>
+    <row r="313" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A313" s="6"/>
+      <c r="B313" s="7"/>
+      <c r="C313" s="192"/>
+      <c r="D313" s="7"/>
+      <c r="E313" s="189"/>
+      <c r="F313" s="192"/>
+      <c r="G313" s="7"/>
+      <c r="H313" s="192"/>
+      <c r="I313" s="192"/>
+      <c r="J313" s="192"/>
+      <c r="K313" s="192"/>
+      <c r="L313" s="7"/>
+      <c r="M313" s="7"/>
+      <c r="N313" s="7"/>
+      <c r="O313" s="7"/>
+      <c r="P313" s="7"/>
+      <c r="Q313" s="7"/>
+      <c r="R313" s="90"/>
+    </row>
+    <row r="314" spans="1:18" ht="14.4" customHeight="1">
+      <c r="A314" s="85"/>
+      <c r="B314" s="86"/>
+      <c r="C314" s="193"/>
+      <c r="D314" s="86"/>
+      <c r="E314" s="86"/>
+      <c r="F314" s="193"/>
+      <c r="G314" s="86"/>
+      <c r="H314" s="193"/>
+      <c r="I314" s="193"/>
+      <c r="J314" s="193"/>
+      <c r="K314" s="193"/>
+      <c r="L314" s="86"/>
+      <c r="M314" s="86"/>
+      <c r="N314" s="86"/>
+      <c r="O314" s="86"/>
+      <c r="P314" s="86"/>
+      <c r="Q314" s="86"/>
+      <c r="R314" s="129"/>
     </row>
     <row r="317" spans="1:18" ht="14.4" customHeight="1">
       <c r="C317" s="276"/>
@@ -30500,6 +30779,12 @@
     </row>
     <row r="324" spans="3:3" ht="14.4" customHeight="1">
       <c r="C324" s="276"/>
+    </row>
+    <row r="325" spans="3:3" ht="14.4" customHeight="1">
+      <c r="C325" s="276"/>
+    </row>
+    <row r="326" spans="3:3" ht="14.4" customHeight="1">
+      <c r="C326" s="276"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30553,6 +30838,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A68A96D9EA1D9545B6EFAC7C8387E0F1" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0d13b557246e747723a516aa573a1fbd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4d36658-c2d2-4aca-88d8-9ecde1689242" xmlns:ns3="b293f0a2-03ef-45d5-a257-c7b71ce04207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90407ce9be83cd6c392ee726c6e0a5b5" ns2:_="" ns3:_="">
     <xsd:import namespace="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
@@ -30793,7 +31089,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -30802,18 +31098,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b293f0a2-03ef-45d5-a257-c7b71ce04207" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4d36658-c2d2-4aca-88d8-9ecde1689242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
+    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BA7FD74-EE25-42EE-BD44-8280994753BD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30832,21 +31128,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFD7C76-261C-4E63-87C5-46C72E1252D3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{018CF3F6-4F5F-42B6-A56D-9E67FD3944EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b293f0a2-03ef-45d5-a257-c7b71ce04207"/>
-    <ds:schemaRef ds:uri="f4d36658-c2d2-4aca-88d8-9ecde1689242"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>